--- a/artfynd/A 7913-2025 artfynd.xlsx
+++ b/artfynd/A 7913-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129963682</v>
+        <v>129963806</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435075</v>
+        <v>434862</v>
       </c>
       <c r="R2" t="n">
-        <v>6783207</v>
+        <v>6783373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129963785</v>
+        <v>129963768</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>78842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435286</v>
+        <v>435080</v>
       </c>
       <c r="R3" t="n">
-        <v>6783280</v>
+        <v>6783283</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129963715</v>
+        <v>129963799</v>
       </c>
       <c r="B4" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434862</v>
+        <v>435115</v>
       </c>
       <c r="R4" t="n">
-        <v>6783371</v>
+        <v>6783224</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129963800</v>
+        <v>129963684</v>
       </c>
       <c r="B5" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435261</v>
+        <v>435069</v>
       </c>
       <c r="R5" t="n">
-        <v>6783290</v>
+        <v>6783183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129963697</v>
+        <v>129963800</v>
       </c>
       <c r="B6" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435140</v>
+        <v>435261</v>
       </c>
       <c r="R6" t="n">
-        <v>6783274</v>
+        <v>6783290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129963799</v>
+        <v>129963697</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435115</v>
+        <v>435140</v>
       </c>
       <c r="R7" t="n">
-        <v>6783224</v>
+        <v>6783274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129963768</v>
+        <v>129963715</v>
       </c>
       <c r="B8" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435080</v>
+        <v>434862</v>
       </c>
       <c r="R8" t="n">
-        <v>6783283</v>
+        <v>6783371</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129963684</v>
+        <v>129963682</v>
       </c>
       <c r="B9" t="n">
         <v>79703</v>
@@ -1399,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435069</v>
+        <v>435075</v>
       </c>
       <c r="R9" t="n">
-        <v>6783183</v>
+        <v>6783207</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,45 +1556,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129963806</v>
+        <v>129963785</v>
       </c>
       <c r="B11" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434862</v>
+        <v>435286</v>
       </c>
       <c r="R11" t="n">
-        <v>6783373</v>
+        <v>6783280</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,6 +1644,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129963775</v>
+        <v>129963838</v>
       </c>
       <c r="B13" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1776,34 +1776,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434969</v>
+        <v>435131</v>
       </c>
       <c r="R13" t="n">
-        <v>6783298</v>
+        <v>6783363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,12 +1841,18 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1862,7 +1871,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129963760</v>
+        <v>129963775</v>
       </c>
       <c r="B14" t="n">
         <v>78842</v>
@@ -1897,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435131</v>
+        <v>434969</v>
       </c>
       <c r="R14" t="n">
-        <v>6783264</v>
+        <v>6783298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1968,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129963774</v>
+        <v>129963760</v>
       </c>
       <c r="B15" t="n">
         <v>78842</v>
@@ -1994,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435002</v>
+        <v>435131</v>
       </c>
       <c r="R15" t="n">
-        <v>6783410</v>
+        <v>6783264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129963838</v>
+        <v>129963774</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,37 +2076,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435131</v>
+        <v>435002</v>
       </c>
       <c r="R16" t="n">
-        <v>6783363</v>
+        <v>6783410</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,18 +2138,12 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2366,45 +2366,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129963830</v>
+        <v>129963784</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435195</v>
+        <v>435269</v>
       </c>
       <c r="R19" t="n">
-        <v>6783259</v>
+        <v>6783269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,6 +2454,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2657,10 +2667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129963798</v>
+        <v>129963849</v>
       </c>
       <c r="B22" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2668,21 +2678,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2692,10 +2702,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435226</v>
+        <v>434989</v>
       </c>
       <c r="R22" t="n">
-        <v>6783162</v>
+        <v>6783322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2754,54 +2764,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129963784</v>
+        <v>129963830</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435269</v>
+        <v>435195</v>
       </c>
       <c r="R23" t="n">
-        <v>6783269</v>
+        <v>6783259</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2842,7 +2843,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129963758</v>
+        <v>129963798</v>
       </c>
       <c r="B24" t="n">
-        <v>78842</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435121</v>
+        <v>435226</v>
       </c>
       <c r="R24" t="n">
-        <v>6783166</v>
+        <v>6783162</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129963849</v>
+        <v>129963758</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434989</v>
+        <v>435121</v>
       </c>
       <c r="R25" t="n">
-        <v>6783322</v>
+        <v>6783166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129963714</v>
+        <v>129963770</v>
       </c>
       <c r="B26" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,21 +3066,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434952</v>
+        <v>435151</v>
       </c>
       <c r="R26" t="n">
-        <v>6783307</v>
+        <v>6783386</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129963770</v>
+        <v>129963723</v>
       </c>
       <c r="B27" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3163,21 +3163,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435151</v>
+        <v>435137</v>
       </c>
       <c r="R27" t="n">
-        <v>6783386</v>
+        <v>6783270</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129963827</v>
+        <v>129963831</v>
       </c>
       <c r="B28" t="n">
         <v>79084</v>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435224</v>
+        <v>435239</v>
       </c>
       <c r="R28" t="n">
-        <v>6783121</v>
+        <v>6783254</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963739</v>
+        <v>129963714</v>
       </c>
       <c r="B29" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3357,42 +3357,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435244</v>
+        <v>434952</v>
       </c>
       <c r="R29" t="n">
-        <v>6783276</v>
+        <v>6783307</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3451,10 +3443,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963723</v>
+        <v>129963827</v>
       </c>
       <c r="B30" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3454,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3478,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435137</v>
+        <v>435224</v>
       </c>
       <c r="R30" t="n">
-        <v>6783270</v>
+        <v>6783121</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129963831</v>
+        <v>129963739</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3661,34 +3653,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435239</v>
+        <v>435244</v>
       </c>
       <c r="R32" t="n">
-        <v>6783254</v>
+        <v>6783276</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129963762</v>
+        <v>129963842</v>
       </c>
       <c r="B33" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435102</v>
+        <v>435074</v>
       </c>
       <c r="R33" t="n">
-        <v>6783245</v>
+        <v>6783347</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,6 +3818,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3844,10 +3849,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129963842</v>
+        <v>129963803</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3860,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435074</v>
+        <v>435063</v>
       </c>
       <c r="R34" t="n">
-        <v>6783347</v>
+        <v>6783239</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,11 +3920,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,10 +3946,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129963803</v>
+        <v>129963834</v>
       </c>
       <c r="B35" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435063</v>
+        <v>435136</v>
       </c>
       <c r="R35" t="n">
-        <v>6783239</v>
+        <v>6783253</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4017,6 +4017,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129963719</v>
+        <v>129963762</v>
       </c>
       <c r="B36" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4059,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435236</v>
+        <v>435102</v>
       </c>
       <c r="R36" t="n">
-        <v>6783256</v>
+        <v>6783245</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4145,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129963834</v>
+        <v>129963719</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4156,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435136</v>
+        <v>435236</v>
       </c>
       <c r="R37" t="n">
-        <v>6783253</v>
+        <v>6783256</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4211,11 +4216,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4554,45 +4554,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129963705</v>
+        <v>129963789</v>
       </c>
       <c r="B41" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435151</v>
+        <v>435157</v>
       </c>
       <c r="R41" t="n">
-        <v>6783380</v>
+        <v>6783283</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4633,6 +4642,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4748,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129963738</v>
+        <v>129963705</v>
       </c>
       <c r="B43" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4759,42 +4769,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435231</v>
+        <v>435151</v>
       </c>
       <c r="R43" t="n">
-        <v>6783171</v>
+        <v>6783380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,10 +4855,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129963750</v>
+        <v>129963738</v>
       </c>
       <c r="B44" t="n">
-        <v>78842</v>
+        <v>57734</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4864,34 +4866,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435002</v>
+        <v>435231</v>
       </c>
       <c r="R44" t="n">
-        <v>6783275</v>
+        <v>6783171</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4950,41 +4960,40 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129963789</v>
+        <v>129963743</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -4994,10 +5003,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435157</v>
+        <v>434936</v>
       </c>
       <c r="R45" t="n">
-        <v>6783283</v>
+        <v>6783319</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5038,7 +5047,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5057,7 +5065,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129963743</v>
+        <v>129963737</v>
       </c>
       <c r="B46" t="n">
         <v>57734</v>
@@ -5100,10 +5108,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434936</v>
+        <v>435238</v>
       </c>
       <c r="R46" t="n">
-        <v>6783319</v>
+        <v>6783110</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5162,10 +5170,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129963737</v>
+        <v>129963750</v>
       </c>
       <c r="B47" t="n">
-        <v>57734</v>
+        <v>78842</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5173,42 +5181,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435238</v>
+        <v>435002</v>
       </c>
       <c r="R47" t="n">
-        <v>6783110</v>
+        <v>6783275</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129963804</v>
+        <v>129963801</v>
       </c>
       <c r="B49" t="n">
         <v>78841</v>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435116</v>
+        <v>435140</v>
       </c>
       <c r="R49" t="n">
-        <v>6783395</v>
+        <v>6783274</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5558,54 +5558,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129963858</v>
+        <v>129963804</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>78841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434900</v>
+        <v>435116</v>
       </c>
       <c r="R51" t="n">
-        <v>6783402</v>
+        <v>6783395</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5646,7 +5637,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5762,10 +5752,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129963801</v>
+        <v>129963718</v>
       </c>
       <c r="B53" t="n">
-        <v>78841</v>
+        <v>79674</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5773,21 +5763,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5797,10 +5787,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435140</v>
+        <v>435195</v>
       </c>
       <c r="R53" t="n">
-        <v>6783274</v>
+        <v>6783256</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5859,45 +5849,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129963718</v>
+        <v>129963858</v>
       </c>
       <c r="B54" t="n">
-        <v>79674</v>
+        <v>8439</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>106554</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435195</v>
+        <v>434900</v>
       </c>
       <c r="R54" t="n">
-        <v>6783256</v>
+        <v>6783402</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5938,6 +5937,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129963696</v>
+        <v>129963708</v>
       </c>
       <c r="B55" t="n">
         <v>79703</v>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435135</v>
+        <v>435013</v>
       </c>
       <c r="R55" t="n">
-        <v>6783269</v>
+        <v>6783367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6053,54 +6053,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129963856</v>
+        <v>129963846</v>
       </c>
       <c r="B56" t="n">
-        <v>5177</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435075</v>
+        <v>435021</v>
       </c>
       <c r="R56" t="n">
-        <v>6783111</v>
+        <v>6783388</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6141,7 +6132,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6160,10 +6150,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129963782</v>
+        <v>129963856</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>5177</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6171,21 +6161,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6204,10 +6194,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435240</v>
+        <v>435075</v>
       </c>
       <c r="R57" t="n">
-        <v>6783151</v>
+        <v>6783111</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,10 +6257,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129963846</v>
+        <v>129963696</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6278,21 +6268,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6302,10 +6292,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435021</v>
+        <v>435135</v>
       </c>
       <c r="R58" t="n">
-        <v>6783388</v>
+        <v>6783269</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6364,10 +6354,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129963749</v>
+        <v>129963681</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6375,21 +6365,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6399,10 +6389,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434946</v>
+        <v>435046</v>
       </c>
       <c r="R59" t="n">
-        <v>6783406</v>
+        <v>6783227</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6461,10 +6451,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129963708</v>
+        <v>129963746</v>
       </c>
       <c r="B60" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6472,34 +6462,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435013</v>
+        <v>434861</v>
       </c>
       <c r="R60" t="n">
-        <v>6783367</v>
+        <v>6783366</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6558,45 +6556,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129963763</v>
+        <v>129963782</v>
       </c>
       <c r="B61" t="n">
-        <v>78842</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435052</v>
+        <v>435240</v>
       </c>
       <c r="R61" t="n">
-        <v>6783227</v>
+        <v>6783151</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6637,6 +6644,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6655,10 +6663,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129963720</v>
+        <v>129963749</v>
       </c>
       <c r="B62" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6666,21 +6674,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6690,10 +6698,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435263</v>
+        <v>434946</v>
       </c>
       <c r="R62" t="n">
-        <v>6783286</v>
+        <v>6783406</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6752,10 +6760,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129963681</v>
+        <v>129963763</v>
       </c>
       <c r="B63" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6763,21 +6771,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6787,7 +6795,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435046</v>
+        <v>435052</v>
       </c>
       <c r="R63" t="n">
         <v>6783227</v>
@@ -6849,10 +6857,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129963753</v>
+        <v>129963720</v>
       </c>
       <c r="B64" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6860,21 +6868,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6884,10 +6892,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435074</v>
+        <v>435263</v>
       </c>
       <c r="R64" t="n">
-        <v>6783208</v>
+        <v>6783286</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6946,10 +6954,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129963727</v>
+        <v>129963753</v>
       </c>
       <c r="B65" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6957,21 +6965,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6981,10 +6989,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>435156</v>
+        <v>435074</v>
       </c>
       <c r="R65" t="n">
-        <v>6783404</v>
+        <v>6783208</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7043,10 +7051,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129963746</v>
+        <v>129963727</v>
       </c>
       <c r="B66" t="n">
-        <v>57734</v>
+        <v>79674</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7054,42 +7062,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434861</v>
+        <v>435156</v>
       </c>
       <c r="R66" t="n">
-        <v>6783366</v>
+        <v>6783404</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7148,10 +7148,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129963701</v>
+        <v>129963837</v>
       </c>
       <c r="B67" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7159,21 +7159,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435051</v>
+        <v>435094</v>
       </c>
       <c r="R67" t="n">
-        <v>6783226</v>
+        <v>6783352</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129963837</v>
+        <v>129963688</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7256,21 +7256,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435094</v>
+        <v>435226</v>
       </c>
       <c r="R68" t="n">
-        <v>6783352</v>
+        <v>6783162</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,10 +7342,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129963761</v>
+        <v>129963707</v>
       </c>
       <c r="B69" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7353,21 +7353,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7377,10 +7377,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435140</v>
+        <v>435035</v>
       </c>
       <c r="R69" t="n">
-        <v>6783272</v>
+        <v>6783349</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7439,10 +7439,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129963735</v>
+        <v>129963701</v>
       </c>
       <c r="B70" t="n">
-        <v>57895</v>
+        <v>79703</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7450,42 +7450,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435028</v>
+        <v>435051</v>
       </c>
       <c r="R70" t="n">
-        <v>6783350</v>
+        <v>6783226</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7544,45 +7536,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129963764</v>
+        <v>129963748</v>
       </c>
       <c r="B71" t="n">
-        <v>78842</v>
+        <v>56930</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435059</v>
+        <v>435072</v>
       </c>
       <c r="R71" t="n">
-        <v>6783248</v>
+        <v>6783347</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129963707</v>
+        <v>129963735</v>
       </c>
       <c r="B72" t="n">
-        <v>79703</v>
+        <v>57895</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7652,34 +7652,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435035</v>
+        <v>435028</v>
       </c>
       <c r="R72" t="n">
-        <v>6783349</v>
+        <v>6783350</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7738,10 +7746,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129963688</v>
+        <v>129963761</v>
       </c>
       <c r="B73" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7749,21 +7757,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7773,10 +7781,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435226</v>
+        <v>435140</v>
       </c>
       <c r="R73" t="n">
-        <v>6783162</v>
+        <v>6783272</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7835,10 +7843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129963728</v>
+        <v>129963764</v>
       </c>
       <c r="B74" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7846,21 +7854,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7870,10 +7878,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435152</v>
+        <v>435059</v>
       </c>
       <c r="R74" t="n">
-        <v>6783393</v>
+        <v>6783248</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7932,53 +7940,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129963748</v>
+        <v>129963728</v>
       </c>
       <c r="B75" t="n">
-        <v>56930</v>
+        <v>79674</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435072</v>
+        <v>435152</v>
       </c>
       <c r="R75" t="n">
-        <v>6783347</v>
+        <v>6783393</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8134,10 +8134,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129963853</v>
+        <v>129963704</v>
       </c>
       <c r="B77" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8145,37 +8145,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434958</v>
+        <v>435073</v>
       </c>
       <c r="R77" t="n">
-        <v>6783365</v>
+        <v>6783319</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8216,7 +8213,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8235,43 +8231,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129963781</v>
+        <v>129963853</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8279,10 +8269,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435073</v>
+        <v>434958</v>
       </c>
       <c r="R78" t="n">
-        <v>6783120</v>
+        <v>6783365</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8439,35 +8429,44 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129963704</v>
+        <v>129963781</v>
       </c>
       <c r="B80" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
@@ -8477,7 +8476,7 @@
         <v>435073</v>
       </c>
       <c r="R80" t="n">
-        <v>6783319</v>
+        <v>6783120</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8518,6 +8517,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8827,54 +8827,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129963779</v>
+        <v>129963829</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434963</v>
+        <v>435142</v>
       </c>
       <c r="R84" t="n">
-        <v>6783366</v>
+        <v>6783234</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8909,13 +8900,17 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -8934,10 +8929,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129963765</v>
+        <v>129963713</v>
       </c>
       <c r="B85" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8945,21 +8940,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8969,10 +8964,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435080</v>
+        <v>434963</v>
       </c>
       <c r="R85" t="n">
-        <v>6783254</v>
+        <v>6783297</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9031,35 +9026,44 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129963713</v>
+        <v>129963779</v>
       </c>
       <c r="B86" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
@@ -9069,7 +9073,7 @@
         <v>434963</v>
       </c>
       <c r="R86" t="n">
-        <v>6783297</v>
+        <v>6783366</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9110,6 +9114,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9128,10 +9133,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129963829</v>
+        <v>129963765</v>
       </c>
       <c r="B87" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9139,21 +9144,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9163,10 +9168,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435142</v>
+        <v>435080</v>
       </c>
       <c r="R87" t="n">
-        <v>6783234</v>
+        <v>6783254</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9199,11 +9204,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9230,7 +9230,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129963710</v>
+        <v>129963692</v>
       </c>
       <c r="B88" t="n">
         <v>79703</v>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>435047</v>
+        <v>435238</v>
       </c>
       <c r="R88" t="n">
-        <v>6783384</v>
+        <v>6783256</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9327,54 +9327,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129963794</v>
+        <v>129963691</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434903</v>
+        <v>435115</v>
       </c>
       <c r="R89" t="n">
-        <v>6783388</v>
+        <v>6783224</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9415,7 +9406,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9434,7 +9424,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129963825</v>
+        <v>129963832</v>
       </c>
       <c r="B90" t="n">
         <v>79084</v>
@@ -9469,10 +9459,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>435247</v>
+        <v>435150</v>
       </c>
       <c r="R90" t="n">
-        <v>6783126</v>
+        <v>6783272</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9531,7 +9521,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129963832</v>
+        <v>129963825</v>
       </c>
       <c r="B91" t="n">
         <v>79084</v>
@@ -9566,10 +9556,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>435150</v>
+        <v>435247</v>
       </c>
       <c r="R91" t="n">
-        <v>6783272</v>
+        <v>6783126</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9628,7 +9618,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129963691</v>
+        <v>129963710</v>
       </c>
       <c r="B92" t="n">
         <v>79703</v>
@@ -9663,10 +9653,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435115</v>
+        <v>435047</v>
       </c>
       <c r="R92" t="n">
-        <v>6783224</v>
+        <v>6783384</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9725,45 +9715,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129963692</v>
+        <v>129963794</v>
       </c>
       <c r="B93" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>435238</v>
+        <v>434903</v>
       </c>
       <c r="R93" t="n">
-        <v>6783256</v>
+        <v>6783388</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9804,6 +9803,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9919,7 +9919,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129963686</v>
+        <v>129963680</v>
       </c>
       <c r="B95" t="n">
         <v>79703</v>
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>435088</v>
+        <v>434999</v>
       </c>
       <c r="R95" t="n">
-        <v>6783097</v>
+        <v>6783278</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129963745</v>
+        <v>129963686</v>
       </c>
       <c r="B97" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10124,42 +10124,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434942</v>
+        <v>435088</v>
       </c>
       <c r="R97" t="n">
-        <v>6783348</v>
+        <v>6783097</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10218,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129963744</v>
+        <v>129963802</v>
       </c>
       <c r="B98" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10229,42 +10221,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434931</v>
+        <v>435056</v>
       </c>
       <c r="R98" t="n">
-        <v>6783336</v>
+        <v>6783229</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10323,10 +10307,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129963680</v>
+        <v>129963745</v>
       </c>
       <c r="B99" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10334,34 +10318,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434999</v>
+        <v>434942</v>
       </c>
       <c r="R99" t="n">
-        <v>6783278</v>
+        <v>6783348</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10420,10 +10412,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129963757</v>
+        <v>129963744</v>
       </c>
       <c r="B100" t="n">
-        <v>78842</v>
+        <v>57734</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10431,34 +10423,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>435226</v>
+        <v>434931</v>
       </c>
       <c r="R100" t="n">
-        <v>6783162</v>
+        <v>6783336</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10517,7 +10517,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129963777</v>
+        <v>129963757</v>
       </c>
       <c r="B101" t="n">
         <v>78842</v>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434863</v>
+        <v>435226</v>
       </c>
       <c r="R101" t="n">
-        <v>6783373</v>
+        <v>6783162</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10614,10 +10614,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129963802</v>
+        <v>129963777</v>
       </c>
       <c r="B102" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10625,21 +10625,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>435056</v>
+        <v>434863</v>
       </c>
       <c r="R102" t="n">
-        <v>6783229</v>
+        <v>6783373</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10711,10 +10711,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129963752</v>
+        <v>129963747</v>
       </c>
       <c r="B103" t="n">
-        <v>78842</v>
+        <v>56310</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10722,34 +10722,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>206004</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>435046</v>
+        <v>435173</v>
       </c>
       <c r="R103" t="n">
-        <v>6783227</v>
+        <v>6783096</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10808,7 +10816,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129963687</v>
+        <v>129963712</v>
       </c>
       <c r="B104" t="n">
         <v>79703</v>
@@ -10843,10 +10851,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>435243</v>
+        <v>434998</v>
       </c>
       <c r="R104" t="n">
-        <v>6783165</v>
+        <v>6783407</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10905,54 +10913,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129963791</v>
+        <v>129963821</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>435076</v>
+        <v>435042</v>
       </c>
       <c r="R105" t="n">
-        <v>6783364</v>
+        <v>6783226</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10993,7 +10992,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11012,10 +11010,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129963821</v>
+        <v>129963687</v>
       </c>
       <c r="B106" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11023,21 +11021,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11047,10 +11045,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>435042</v>
+        <v>435243</v>
       </c>
       <c r="R106" t="n">
-        <v>6783226</v>
+        <v>6783165</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11109,45 +11107,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129963754</v>
+        <v>129963791</v>
       </c>
       <c r="B107" t="n">
-        <v>78842</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>435094</v>
+        <v>435076</v>
       </c>
       <c r="R107" t="n">
-        <v>6783192</v>
+        <v>6783364</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11188,6 +11195,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11206,10 +11214,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129963747</v>
+        <v>129963752</v>
       </c>
       <c r="B108" t="n">
-        <v>56310</v>
+        <v>78842</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11217,42 +11225,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>206004</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>435173</v>
+        <v>435046</v>
       </c>
       <c r="R108" t="n">
-        <v>6783096</v>
+        <v>6783227</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11311,10 +11311,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129963712</v>
+        <v>129963754</v>
       </c>
       <c r="B109" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11322,21 +11322,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11346,10 +11346,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434998</v>
+        <v>435094</v>
       </c>
       <c r="R109" t="n">
-        <v>6783407</v>
+        <v>6783192</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11408,10 +11408,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129963835</v>
+        <v>129963772</v>
       </c>
       <c r="B110" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11419,21 +11419,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>435082</v>
+        <v>435050</v>
       </c>
       <c r="R110" t="n">
-        <v>6783221</v>
+        <v>6783382</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11479,11 +11479,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11510,10 +11505,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129963772</v>
+        <v>129963835</v>
       </c>
       <c r="B111" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11521,21 +11516,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11545,10 +11540,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>435050</v>
+        <v>435082</v>
       </c>
       <c r="R111" t="n">
-        <v>6783382</v>
+        <v>6783221</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11581,6 +11576,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11811,7 +11811,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129963852</v>
+        <v>129963844</v>
       </c>
       <c r="B114" t="n">
         <v>79084</v>
@@ -11846,10 +11846,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434938</v>
+        <v>435038</v>
       </c>
       <c r="R114" t="n">
-        <v>6783373</v>
+        <v>6783417</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11882,6 +11882,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11908,7 +11913,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129963693</v>
+        <v>129963698</v>
       </c>
       <c r="B115" t="n">
         <v>79703</v>
@@ -11943,10 +11948,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>435260</v>
+        <v>435103</v>
       </c>
       <c r="R115" t="n">
-        <v>6783290</v>
+        <v>6783246</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12005,10 +12010,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129963740</v>
+        <v>129963852</v>
       </c>
       <c r="B116" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12016,42 +12021,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>435041</v>
+        <v>434938</v>
       </c>
       <c r="R116" t="n">
-        <v>6783374</v>
+        <v>6783373</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12110,54 +12107,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129963790</v>
+        <v>129963693</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>435100</v>
+        <v>435260</v>
       </c>
       <c r="R117" t="n">
-        <v>6783252</v>
+        <v>6783290</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12198,7 +12186,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12217,10 +12204,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129963844</v>
+        <v>129963740</v>
       </c>
       <c r="B118" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12228,34 +12215,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435038</v>
+        <v>435041</v>
       </c>
       <c r="R118" t="n">
-        <v>6783417</v>
+        <v>6783374</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12288,11 +12283,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12319,45 +12309,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129963698</v>
+        <v>129963790</v>
       </c>
       <c r="B119" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435103</v>
+        <v>435100</v>
       </c>
       <c r="R119" t="n">
-        <v>6783246</v>
+        <v>6783252</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12398,6 +12397,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129963751</v>
+        <v>129963805</v>
       </c>
       <c r="B120" t="n">
-        <v>78842</v>
+        <v>78841</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434998</v>
+        <v>435113</v>
       </c>
       <c r="R120" t="n">
-        <v>6783271</v>
+        <v>6783386</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12618,54 +12618,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129963780</v>
+        <v>129963845</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>435085</v>
+        <v>435002</v>
       </c>
       <c r="R122" t="n">
-        <v>6783160</v>
+        <v>6783412</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12706,7 +12697,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12725,45 +12715,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129963845</v>
+        <v>129963780</v>
       </c>
       <c r="B123" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>435002</v>
+        <v>435085</v>
       </c>
       <c r="R123" t="n">
-        <v>6783412</v>
+        <v>6783160</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12804,6 +12803,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12822,10 +12822,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129963722</v>
+        <v>129963751</v>
       </c>
       <c r="B124" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12833,21 +12833,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>435197</v>
+        <v>434998</v>
       </c>
       <c r="R124" t="n">
-        <v>6783294</v>
+        <v>6783271</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129963805</v>
+        <v>129963722</v>
       </c>
       <c r="B125" t="n">
-        <v>78841</v>
+        <v>79674</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12930,21 +12930,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12954,10 +12954,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435113</v>
+        <v>435197</v>
       </c>
       <c r="R125" t="n">
-        <v>6783386</v>
+        <v>6783294</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129963822</v>
+        <v>129963841</v>
       </c>
       <c r="B126" t="n">
         <v>79084</v>
@@ -13051,10 +13051,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>435060</v>
+        <v>435105</v>
       </c>
       <c r="R126" t="n">
-        <v>6783211</v>
+        <v>6783392</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13087,6 +13087,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13113,40 +13118,41 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129963733</v>
+        <v>129963783</v>
       </c>
       <c r="B127" t="n">
-        <v>57895</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -13156,10 +13162,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435055</v>
+        <v>435255</v>
       </c>
       <c r="R127" t="n">
-        <v>6783240</v>
+        <v>6783275</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13200,6 +13206,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13218,7 +13225,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129963841</v>
+        <v>129963822</v>
       </c>
       <c r="B128" t="n">
         <v>79084</v>
@@ -13253,10 +13260,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>435105</v>
+        <v>435060</v>
       </c>
       <c r="R128" t="n">
-        <v>6783392</v>
+        <v>6783211</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13289,11 +13296,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13320,41 +13322,40 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129963783</v>
+        <v>129963733</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>57895</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -13364,10 +13365,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435255</v>
+        <v>435055</v>
       </c>
       <c r="R129" t="n">
-        <v>6783275</v>
+        <v>6783240</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13408,7 +13409,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13427,10 +13427,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129963709</v>
+        <v>129963839</v>
       </c>
       <c r="B130" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13438,21 +13438,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>435050</v>
+        <v>435149</v>
       </c>
       <c r="R130" t="n">
-        <v>6783376</v>
+        <v>6783386</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13498,6 +13498,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13524,54 +13529,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129963787</v>
+        <v>129963709</v>
       </c>
       <c r="B131" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>435226</v>
+        <v>435050</v>
       </c>
       <c r="R131" t="n">
-        <v>6783309</v>
+        <v>6783376</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13612,7 +13608,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13631,45 +13626,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129963839</v>
+        <v>129963787</v>
       </c>
       <c r="B132" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>435149</v>
+        <v>435226</v>
       </c>
       <c r="R132" t="n">
-        <v>6783386</v>
+        <v>6783309</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13704,17 +13708,13 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13733,7 +13733,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129963699</v>
+        <v>129963702</v>
       </c>
       <c r="B133" t="n">
         <v>79703</v>
@@ -13768,10 +13768,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>435081</v>
+        <v>435064</v>
       </c>
       <c r="R133" t="n">
-        <v>6783223</v>
+        <v>6783239</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13830,10 +13830,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129963756</v>
+        <v>129963851</v>
       </c>
       <c r="B134" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13841,21 +13841,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>435087</v>
+        <v>434938</v>
       </c>
       <c r="R134" t="n">
-        <v>6783099</v>
+        <v>6783327</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13927,7 +13927,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129963683</v>
+        <v>129963699</v>
       </c>
       <c r="B135" t="n">
         <v>79703</v>
@@ -13962,10 +13962,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>435093</v>
+        <v>435081</v>
       </c>
       <c r="R135" t="n">
-        <v>6783192</v>
+        <v>6783223</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129963725</v>
+        <v>129963836</v>
       </c>
       <c r="B136" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14035,21 +14035,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>435062</v>
+        <v>435073</v>
       </c>
       <c r="R136" t="n">
-        <v>6783268</v>
+        <v>6783270</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14095,6 +14095,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14315,10 +14320,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129963769</v>
+        <v>129963828</v>
       </c>
       <c r="B139" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14326,21 +14331,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14350,10 +14355,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>435072</v>
+        <v>435102</v>
       </c>
       <c r="R139" t="n">
-        <v>6783317</v>
+        <v>6783177</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14386,6 +14391,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14412,10 +14422,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129963828</v>
+        <v>129963683</v>
       </c>
       <c r="B140" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14423,21 +14433,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14447,10 +14457,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>435102</v>
+        <v>435093</v>
       </c>
       <c r="R140" t="n">
-        <v>6783177</v>
+        <v>6783192</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14483,11 +14493,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14514,10 +14519,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129963851</v>
+        <v>129963756</v>
       </c>
       <c r="B141" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14525,21 +14530,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14549,10 +14554,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>434938</v>
+        <v>435087</v>
       </c>
       <c r="R141" t="n">
-        <v>6783327</v>
+        <v>6783099</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14611,10 +14616,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129963836</v>
+        <v>129963725</v>
       </c>
       <c r="B142" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14622,21 +14627,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14646,10 +14651,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>435073</v>
+        <v>435062</v>
       </c>
       <c r="R142" t="n">
-        <v>6783270</v>
+        <v>6783268</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14682,11 +14687,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14713,10 +14713,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129963702</v>
+        <v>129963769</v>
       </c>
       <c r="B143" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14724,21 +14724,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14748,10 +14748,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>435064</v>
+        <v>435072</v>
       </c>
       <c r="R143" t="n">
-        <v>6783239</v>
+        <v>6783317</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 7913-2025 artfynd.xlsx
+++ b/artfynd/A 7913-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129963806</v>
+        <v>129963742</v>
       </c>
       <c r="B2" t="n">
-        <v>78841</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434862</v>
+        <v>434938</v>
       </c>
       <c r="R2" t="n">
-        <v>6783373</v>
+        <v>6783317</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129963768</v>
+        <v>129963682</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435080</v>
+        <v>435075</v>
       </c>
       <c r="R3" t="n">
-        <v>6783283</v>
+        <v>6783207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129963799</v>
+        <v>129963715</v>
       </c>
       <c r="B4" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435115</v>
+        <v>434862</v>
       </c>
       <c r="R4" t="n">
-        <v>6783224</v>
+        <v>6783371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129963684</v>
+        <v>129963800</v>
       </c>
       <c r="B5" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435069</v>
+        <v>435261</v>
       </c>
       <c r="R5" t="n">
-        <v>6783183</v>
+        <v>6783290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129963800</v>
+        <v>129963697</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435261</v>
+        <v>435140</v>
       </c>
       <c r="R6" t="n">
-        <v>6783290</v>
+        <v>6783274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129963697</v>
+        <v>129963799</v>
       </c>
       <c r="B7" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435140</v>
+        <v>435115</v>
       </c>
       <c r="R7" t="n">
-        <v>6783274</v>
+        <v>6783224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1265,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129963715</v>
+        <v>129963684</v>
       </c>
       <c r="B8" t="n">
         <v>79703</v>
@@ -1292,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434862</v>
+        <v>435069</v>
       </c>
       <c r="R8" t="n">
-        <v>6783371</v>
+        <v>6783183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129963682</v>
+        <v>129963806</v>
       </c>
       <c r="B9" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435075</v>
+        <v>434862</v>
       </c>
       <c r="R9" t="n">
-        <v>6783207</v>
+        <v>6783373</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129963742</v>
+        <v>129963768</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>78842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,42 +1470,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434938</v>
+        <v>435080</v>
       </c>
       <c r="R10" t="n">
-        <v>6783317</v>
+        <v>6783283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129963843</v>
+        <v>129963775</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435037</v>
+        <v>434969</v>
       </c>
       <c r="R12" t="n">
-        <v>6783350</v>
+        <v>6783298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1734,11 +1734,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1765,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129963838</v>
+        <v>129963760</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1776,27 +1771,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
@@ -1806,7 +1798,7 @@
         <v>435131</v>
       </c>
       <c r="R13" t="n">
-        <v>6783363</v>
+        <v>6783264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,18 +1833,12 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1871,7 +1857,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129963775</v>
+        <v>129963774</v>
       </c>
       <c r="B14" t="n">
         <v>78842</v>
@@ -1906,10 +1892,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434969</v>
+        <v>435002</v>
       </c>
       <c r="R14" t="n">
-        <v>6783298</v>
+        <v>6783410</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,7 +1954,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129963760</v>
+        <v>129963778</v>
       </c>
       <c r="B15" t="n">
         <v>78842</v>
@@ -2003,10 +1989,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435131</v>
+        <v>434872</v>
       </c>
       <c r="R15" t="n">
-        <v>6783264</v>
+        <v>6783360</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,10 +2051,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129963774</v>
+        <v>129963843</v>
       </c>
       <c r="B16" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2062,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2086,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435002</v>
+        <v>435037</v>
       </c>
       <c r="R16" t="n">
-        <v>6783410</v>
+        <v>6783350</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2136,6 +2122,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2162,10 +2153,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129963778</v>
+        <v>129963838</v>
       </c>
       <c r="B17" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,34 +2164,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434872</v>
+        <v>435131</v>
       </c>
       <c r="R17" t="n">
-        <v>6783360</v>
+        <v>6783363</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,12 +2229,18 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2259,54 +2259,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129963792</v>
+        <v>129963830</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435029</v>
+        <v>435195</v>
       </c>
       <c r="R18" t="n">
-        <v>6783411</v>
+        <v>6783259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2347,7 +2338,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2366,54 +2356,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129963784</v>
+        <v>129963850</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435269</v>
+        <v>434979</v>
       </c>
       <c r="R19" t="n">
-        <v>6783269</v>
+        <v>6783324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2435,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2473,7 +2453,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129963850</v>
+        <v>129963849</v>
       </c>
       <c r="B20" t="n">
         <v>79084</v>
@@ -2508,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434979</v>
+        <v>434989</v>
       </c>
       <c r="R20" t="n">
-        <v>6783324</v>
+        <v>6783322</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,10 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129963849</v>
+        <v>129963798</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2678,21 +2658,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2702,10 +2682,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434989</v>
+        <v>435226</v>
       </c>
       <c r="R22" t="n">
-        <v>6783322</v>
+        <v>6783162</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2764,45 +2744,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129963830</v>
+        <v>129963792</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435195</v>
+        <v>435029</v>
       </c>
       <c r="R23" t="n">
-        <v>6783259</v>
+        <v>6783411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,6 +2832,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2861,45 +2851,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129963798</v>
+        <v>129963784</v>
       </c>
       <c r="B24" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435226</v>
+        <v>435269</v>
       </c>
       <c r="R24" t="n">
-        <v>6783162</v>
+        <v>6783269</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2940,6 +2939,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129963770</v>
+        <v>129963714</v>
       </c>
       <c r="B26" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,21 +3066,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435151</v>
+        <v>434952</v>
       </c>
       <c r="R26" t="n">
-        <v>6783386</v>
+        <v>6783307</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129963723</v>
+        <v>129963739</v>
       </c>
       <c r="B27" t="n">
-        <v>79674</v>
+        <v>57734</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3163,34 +3163,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435137</v>
+        <v>435244</v>
       </c>
       <c r="R27" t="n">
-        <v>6783270</v>
+        <v>6783276</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3249,7 +3257,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129963831</v>
+        <v>129963827</v>
       </c>
       <c r="B28" t="n">
         <v>79084</v>
@@ -3284,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435239</v>
+        <v>435224</v>
       </c>
       <c r="R28" t="n">
-        <v>6783254</v>
+        <v>6783121</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963714</v>
+        <v>129963848</v>
       </c>
       <c r="B29" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3357,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3381,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434952</v>
+        <v>434993</v>
       </c>
       <c r="R29" t="n">
-        <v>6783307</v>
+        <v>6783317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3417,6 +3425,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3443,7 +3456,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963827</v>
+        <v>129963831</v>
       </c>
       <c r="B30" t="n">
         <v>79084</v>
@@ -3478,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435224</v>
+        <v>435239</v>
       </c>
       <c r="R30" t="n">
-        <v>6783121</v>
+        <v>6783254</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3540,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129963848</v>
+        <v>129963770</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3551,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3575,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434993</v>
+        <v>435151</v>
       </c>
       <c r="R31" t="n">
-        <v>6783317</v>
+        <v>6783386</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3611,11 +3624,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3642,10 +3650,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129963739</v>
+        <v>129963723</v>
       </c>
       <c r="B32" t="n">
-        <v>57734</v>
+        <v>79674</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,42 +3661,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435244</v>
+        <v>435137</v>
       </c>
       <c r="R32" t="n">
-        <v>6783276</v>
+        <v>6783270</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129963842</v>
+        <v>129963762</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435074</v>
+        <v>435102</v>
       </c>
       <c r="R33" t="n">
-        <v>6783347</v>
+        <v>6783245</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,11 +3818,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3849,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129963803</v>
+        <v>129963719</v>
       </c>
       <c r="B34" t="n">
-        <v>78841</v>
+        <v>79674</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3860,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435063</v>
+        <v>435236</v>
       </c>
       <c r="R34" t="n">
-        <v>6783239</v>
+        <v>6783256</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3946,10 +3941,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129963834</v>
+        <v>129963724</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3957,21 +3952,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435136</v>
+        <v>435055</v>
       </c>
       <c r="R35" t="n">
-        <v>6783253</v>
+        <v>6783236</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4017,11 +4012,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,7 +4038,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129963762</v>
+        <v>129963767</v>
       </c>
       <c r="B36" t="n">
         <v>78842</v>
@@ -4083,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435102</v>
+        <v>435066</v>
       </c>
       <c r="R36" t="n">
-        <v>6783245</v>
+        <v>6783276</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4145,10 +4135,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129963719</v>
+        <v>129963803</v>
       </c>
       <c r="B37" t="n">
-        <v>79674</v>
+        <v>78841</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4156,21 +4146,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4180,10 +4170,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435236</v>
+        <v>435063</v>
       </c>
       <c r="R37" t="n">
-        <v>6783256</v>
+        <v>6783239</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4242,10 +4232,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129963724</v>
+        <v>129963842</v>
       </c>
       <c r="B38" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4253,21 +4243,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4277,10 +4267,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435055</v>
+        <v>435074</v>
       </c>
       <c r="R38" t="n">
-        <v>6783236</v>
+        <v>6783347</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4313,6 +4303,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4339,10 +4334,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129963767</v>
+        <v>129963834</v>
       </c>
       <c r="B39" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4350,21 +4345,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435066</v>
+        <v>435136</v>
       </c>
       <c r="R39" t="n">
-        <v>6783276</v>
+        <v>6783253</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4410,6 +4405,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4436,45 +4436,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129963731</v>
+        <v>129963738</v>
       </c>
       <c r="B40" t="n">
-        <v>91566</v>
+        <v>57734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434932</v>
+        <v>435231</v>
       </c>
       <c r="R40" t="n">
-        <v>6783346</v>
+        <v>6783171</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4515,29 +4523,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4554,41 +4541,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129963789</v>
+        <v>129963743</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4598,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435157</v>
+        <v>434936</v>
       </c>
       <c r="R41" t="n">
-        <v>6783283</v>
+        <v>6783319</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,7 +4628,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4661,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129963854</v>
+        <v>129963737</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4672,34 +4657,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434905</v>
+        <v>435238</v>
       </c>
       <c r="R42" t="n">
-        <v>6783388</v>
+        <v>6783110</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4758,10 +4751,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129963705</v>
+        <v>129963750</v>
       </c>
       <c r="B43" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4762,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435151</v>
+        <v>435002</v>
       </c>
       <c r="R43" t="n">
-        <v>6783380</v>
+        <v>6783275</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4855,10 +4848,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129963738</v>
+        <v>129963705</v>
       </c>
       <c r="B44" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,42 +4859,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435231</v>
+        <v>435151</v>
       </c>
       <c r="R44" t="n">
-        <v>6783171</v>
+        <v>6783380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4960,53 +4945,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129963743</v>
+        <v>129963731</v>
       </c>
       <c r="B45" t="n">
-        <v>57734</v>
+        <v>91566</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434936</v>
+        <v>434932</v>
       </c>
       <c r="R45" t="n">
-        <v>6783319</v>
+        <v>6783346</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5047,8 +5024,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5065,10 +5063,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129963737</v>
+        <v>129963854</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5076,42 +5074,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435238</v>
+        <v>434905</v>
       </c>
       <c r="R46" t="n">
-        <v>6783110</v>
+        <v>6783388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5170,45 +5160,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129963750</v>
+        <v>129963789</v>
       </c>
       <c r="B47" t="n">
-        <v>78842</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435002</v>
+        <v>435157</v>
       </c>
       <c r="R47" t="n">
-        <v>6783275</v>
+        <v>6783283</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5249,6 +5248,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129963823</v>
+        <v>129963804</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5278,21 +5278,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435065</v>
+        <v>435116</v>
       </c>
       <c r="R48" t="n">
-        <v>6783208</v>
+        <v>6783395</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5364,10 +5364,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129963801</v>
+        <v>129963703</v>
       </c>
       <c r="B49" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5375,21 +5375,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435140</v>
+        <v>435072</v>
       </c>
       <c r="R49" t="n">
-        <v>6783274</v>
+        <v>6783251</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5461,10 +5461,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129963703</v>
+        <v>129963801</v>
       </c>
       <c r="B50" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,21 +5472,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435072</v>
+        <v>435140</v>
       </c>
       <c r="R50" t="n">
-        <v>6783251</v>
+        <v>6783274</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129963804</v>
+        <v>129963823</v>
       </c>
       <c r="B51" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,21 +5569,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435116</v>
+        <v>435065</v>
       </c>
       <c r="R51" t="n">
-        <v>6783395</v>
+        <v>6783208</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5655,45 +5655,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129963759</v>
+        <v>129963858</v>
       </c>
       <c r="B52" t="n">
-        <v>78842</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435138</v>
+        <v>434900</v>
       </c>
       <c r="R52" t="n">
-        <v>6783290</v>
+        <v>6783402</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5734,6 +5743,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5752,10 +5762,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129963718</v>
+        <v>129963759</v>
       </c>
       <c r="B53" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,21 +5773,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5787,10 +5797,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435195</v>
+        <v>435138</v>
       </c>
       <c r="R53" t="n">
-        <v>6783256</v>
+        <v>6783290</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5849,54 +5859,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129963858</v>
+        <v>129963718</v>
       </c>
       <c r="B54" t="n">
-        <v>8439</v>
+        <v>79674</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106554</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434900</v>
+        <v>435195</v>
       </c>
       <c r="R54" t="n">
-        <v>6783402</v>
+        <v>6783256</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5937,7 +5938,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5956,10 +5956,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129963708</v>
+        <v>129963746</v>
       </c>
       <c r="B55" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,34 +5967,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435013</v>
+        <v>434861</v>
       </c>
       <c r="R55" t="n">
-        <v>6783367</v>
+        <v>6783366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6053,45 +6061,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129963846</v>
+        <v>129963856</v>
       </c>
       <c r="B56" t="n">
-        <v>79084</v>
+        <v>5177</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435021</v>
+        <v>435075</v>
       </c>
       <c r="R56" t="n">
-        <v>6783388</v>
+        <v>6783111</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6132,6 +6149,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6150,54 +6168,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129963856</v>
+        <v>129963696</v>
       </c>
       <c r="B57" t="n">
-        <v>5177</v>
+        <v>79703</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435075</v>
+        <v>435135</v>
       </c>
       <c r="R57" t="n">
-        <v>6783111</v>
+        <v>6783269</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6238,7 +6247,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6257,7 +6265,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129963696</v>
+        <v>129963708</v>
       </c>
       <c r="B58" t="n">
         <v>79703</v>
@@ -6292,10 +6300,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435135</v>
+        <v>435013</v>
       </c>
       <c r="R58" t="n">
-        <v>6783269</v>
+        <v>6783367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6451,10 +6459,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129963746</v>
+        <v>129963846</v>
       </c>
       <c r="B60" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6462,42 +6470,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434861</v>
+        <v>435021</v>
       </c>
       <c r="R60" t="n">
-        <v>6783366</v>
+        <v>6783388</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7148,45 +7148,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129963837</v>
+        <v>129963748</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>56930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435094</v>
+        <v>435072</v>
       </c>
       <c r="R67" t="n">
-        <v>6783352</v>
+        <v>6783347</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7245,7 +7253,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129963688</v>
+        <v>129963701</v>
       </c>
       <c r="B68" t="n">
         <v>79703</v>
@@ -7280,10 +7288,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435226</v>
+        <v>435051</v>
       </c>
       <c r="R68" t="n">
-        <v>6783162</v>
+        <v>6783226</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7439,7 +7447,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129963701</v>
+        <v>129963688</v>
       </c>
       <c r="B70" t="n">
         <v>79703</v>
@@ -7474,10 +7482,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435051</v>
+        <v>435226</v>
       </c>
       <c r="R70" t="n">
-        <v>6783226</v>
+        <v>6783162</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7536,53 +7544,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129963748</v>
+        <v>129963837</v>
       </c>
       <c r="B71" t="n">
-        <v>56930</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435072</v>
+        <v>435094</v>
       </c>
       <c r="R71" t="n">
-        <v>6783347</v>
+        <v>6783352</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8037,45 +8037,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129963689</v>
+        <v>129963781</v>
       </c>
       <c r="B76" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>435225</v>
+        <v>435073</v>
       </c>
       <c r="R76" t="n">
-        <v>6783144</v>
+        <v>6783120</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8116,6 +8125,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8134,10 +8144,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129963704</v>
+        <v>129963717</v>
       </c>
       <c r="B77" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8145,21 +8155,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8169,10 +8179,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435073</v>
+        <v>435121</v>
       </c>
       <c r="R77" t="n">
-        <v>6783319</v>
+        <v>6783164</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8231,10 +8241,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129963853</v>
+        <v>129963716</v>
       </c>
       <c r="B78" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8242,37 +8252,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434958</v>
+        <v>435184</v>
       </c>
       <c r="R78" t="n">
-        <v>6783365</v>
+        <v>6783109</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8313,7 +8320,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8332,10 +8338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129963820</v>
+        <v>129963689</v>
       </c>
       <c r="B79" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8343,21 +8349,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8367,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435070</v>
+        <v>435225</v>
       </c>
       <c r="R79" t="n">
-        <v>6783207</v>
+        <v>6783144</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8429,44 +8435,35 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129963781</v>
+        <v>129963704</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
@@ -8476,7 +8473,7 @@
         <v>435073</v>
       </c>
       <c r="R80" t="n">
-        <v>6783120</v>
+        <v>6783319</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8517,7 +8514,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8536,10 +8532,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129963717</v>
+        <v>129963853</v>
       </c>
       <c r="B81" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8547,34 +8543,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435121</v>
+        <v>434958</v>
       </c>
       <c r="R81" t="n">
-        <v>6783164</v>
+        <v>6783365</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8615,6 +8614,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8633,10 +8633,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129963716</v>
+        <v>129963820</v>
       </c>
       <c r="B82" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8644,21 +8644,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435184</v>
+        <v>435070</v>
       </c>
       <c r="R82" t="n">
-        <v>6783109</v>
+        <v>6783207</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129963847</v>
+        <v>129963829</v>
       </c>
       <c r="B83" t="n">
         <v>79084</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435018</v>
+        <v>435142</v>
       </c>
       <c r="R83" t="n">
-        <v>6783344</v>
+        <v>6783234</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8801,6 +8801,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8827,10 +8832,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129963829</v>
+        <v>129963765</v>
       </c>
       <c r="B84" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8838,21 +8843,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8862,10 +8867,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435142</v>
+        <v>435080</v>
       </c>
       <c r="R84" t="n">
-        <v>6783234</v>
+        <v>6783254</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8898,11 +8903,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9026,54 +9026,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129963779</v>
+        <v>129963847</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434963</v>
+        <v>435018</v>
       </c>
       <c r="R86" t="n">
-        <v>6783366</v>
+        <v>6783344</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9114,7 +9105,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9133,45 +9123,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129963765</v>
+        <v>129963779</v>
       </c>
       <c r="B87" t="n">
-        <v>78842</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435080</v>
+        <v>434963</v>
       </c>
       <c r="R87" t="n">
-        <v>6783254</v>
+        <v>6783366</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9212,6 +9211,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9230,45 +9230,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129963692</v>
+        <v>129963794</v>
       </c>
       <c r="B88" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>435238</v>
+        <v>434903</v>
       </c>
       <c r="R88" t="n">
-        <v>6783256</v>
+        <v>6783388</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9309,6 +9318,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9327,10 +9337,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129963691</v>
+        <v>129963825</v>
       </c>
       <c r="B89" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9338,21 +9348,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9362,10 +9372,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>435115</v>
+        <v>435247</v>
       </c>
       <c r="R89" t="n">
-        <v>6783224</v>
+        <v>6783126</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9521,10 +9531,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129963825</v>
+        <v>129963710</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9532,21 +9542,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9556,10 +9566,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>435247</v>
+        <v>435047</v>
       </c>
       <c r="R91" t="n">
-        <v>6783126</v>
+        <v>6783384</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9618,7 +9628,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129963710</v>
+        <v>129963691</v>
       </c>
       <c r="B92" t="n">
         <v>79703</v>
@@ -9653,10 +9663,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435047</v>
+        <v>435115</v>
       </c>
       <c r="R92" t="n">
-        <v>6783384</v>
+        <v>6783224</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9715,54 +9725,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129963794</v>
+        <v>129963692</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434903</v>
+        <v>435238</v>
       </c>
       <c r="R93" t="n">
-        <v>6783388</v>
+        <v>6783256</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9803,7 +9804,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9822,10 +9822,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129963826</v>
+        <v>129963686</v>
       </c>
       <c r="B94" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9833,21 +9833,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>435250</v>
+        <v>435088</v>
       </c>
       <c r="R94" t="n">
-        <v>6783158</v>
+        <v>6783097</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9919,7 +9919,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129963680</v>
+        <v>129963711</v>
       </c>
       <c r="B95" t="n">
         <v>79703</v>
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>434999</v>
+        <v>435000</v>
       </c>
       <c r="R95" t="n">
-        <v>6783278</v>
+        <v>6783432</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10016,7 +10016,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129963711</v>
+        <v>129963680</v>
       </c>
       <c r="B96" t="n">
         <v>79703</v>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>435000</v>
+        <v>434999</v>
       </c>
       <c r="R96" t="n">
-        <v>6783432</v>
+        <v>6783278</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129963686</v>
+        <v>129963802</v>
       </c>
       <c r="B97" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10124,21 +10124,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10148,10 +10148,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>435088</v>
+        <v>435056</v>
       </c>
       <c r="R97" t="n">
-        <v>6783097</v>
+        <v>6783229</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129963802</v>
+        <v>129963826</v>
       </c>
       <c r="B98" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>435056</v>
+        <v>435250</v>
       </c>
       <c r="R98" t="n">
-        <v>6783229</v>
+        <v>6783158</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10711,10 +10711,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129963747</v>
+        <v>129963687</v>
       </c>
       <c r="B103" t="n">
-        <v>56310</v>
+        <v>79703</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10722,42 +10722,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>206004</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>435173</v>
+        <v>435243</v>
       </c>
       <c r="R103" t="n">
-        <v>6783096</v>
+        <v>6783165</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11010,45 +11002,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129963687</v>
+        <v>129963791</v>
       </c>
       <c r="B106" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>435243</v>
+        <v>435076</v>
       </c>
       <c r="R106" t="n">
-        <v>6783165</v>
+        <v>6783364</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11089,6 +11090,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11107,54 +11109,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129963791</v>
+        <v>129963752</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>78842</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>435076</v>
+        <v>435046</v>
       </c>
       <c r="R107" t="n">
-        <v>6783364</v>
+        <v>6783227</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11195,7 +11188,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11214,7 +11206,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129963752</v>
+        <v>129963754</v>
       </c>
       <c r="B108" t="n">
         <v>78842</v>
@@ -11249,10 +11241,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>435046</v>
+        <v>435094</v>
       </c>
       <c r="R108" t="n">
-        <v>6783227</v>
+        <v>6783192</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11311,10 +11303,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129963754</v>
+        <v>129963747</v>
       </c>
       <c r="B109" t="n">
-        <v>78842</v>
+        <v>56310</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11322,34 +11314,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>206004</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>435094</v>
+        <v>435173</v>
       </c>
       <c r="R109" t="n">
-        <v>6783192</v>
+        <v>6783096</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11811,10 +11811,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129963844</v>
+        <v>129963693</v>
       </c>
       <c r="B114" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11822,21 +11822,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11846,10 +11846,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>435038</v>
+        <v>435260</v>
       </c>
       <c r="R114" t="n">
-        <v>6783417</v>
+        <v>6783290</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11882,11 +11882,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12107,10 +12102,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129963693</v>
+        <v>129963844</v>
       </c>
       <c r="B117" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12118,21 +12113,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12142,10 +12137,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>435260</v>
+        <v>435038</v>
       </c>
       <c r="R117" t="n">
-        <v>6783290</v>
+        <v>6783417</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12178,6 +12173,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12204,40 +12204,41 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129963740</v>
+        <v>129963790</v>
       </c>
       <c r="B118" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -12247,10 +12248,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435041</v>
+        <v>435100</v>
       </c>
       <c r="R118" t="n">
-        <v>6783374</v>
+        <v>6783252</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12291,6 +12292,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12309,41 +12311,40 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129963790</v>
+        <v>129963740</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -12353,10 +12354,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435100</v>
+        <v>435041</v>
       </c>
       <c r="R119" t="n">
-        <v>6783252</v>
+        <v>6783374</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12397,7 +12398,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12416,45 +12416,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129963805</v>
+        <v>129963780</v>
       </c>
       <c r="B120" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435113</v>
+        <v>435085</v>
       </c>
       <c r="R120" t="n">
-        <v>6783386</v>
+        <v>6783160</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12495,6 +12504,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12618,10 +12628,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129963845</v>
+        <v>129963805</v>
       </c>
       <c r="B122" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12629,21 +12639,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12653,10 +12663,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>435002</v>
+        <v>435113</v>
       </c>
       <c r="R122" t="n">
-        <v>6783412</v>
+        <v>6783386</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12715,54 +12725,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129963780</v>
+        <v>129963845</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>435085</v>
+        <v>435002</v>
       </c>
       <c r="R123" t="n">
-        <v>6783160</v>
+        <v>6783412</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12803,7 +12804,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129963841</v>
+        <v>129963822</v>
       </c>
       <c r="B126" t="n">
         <v>79084</v>
@@ -13051,10 +13051,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>435105</v>
+        <v>435060</v>
       </c>
       <c r="R126" t="n">
-        <v>6783392</v>
+        <v>6783211</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13087,11 +13087,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13118,54 +13113,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129963783</v>
+        <v>129963841</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435255</v>
+        <v>435105</v>
       </c>
       <c r="R127" t="n">
-        <v>6783275</v>
+        <v>6783392</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13200,13 +13186,17 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13225,10 +13215,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129963822</v>
+        <v>129963733</v>
       </c>
       <c r="B128" t="n">
-        <v>79084</v>
+        <v>57895</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13236,34 +13226,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>435060</v>
+        <v>435055</v>
       </c>
       <c r="R128" t="n">
-        <v>6783211</v>
+        <v>6783240</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13322,40 +13320,41 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129963733</v>
+        <v>129963783</v>
       </c>
       <c r="B129" t="n">
-        <v>57895</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -13365,10 +13364,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435055</v>
+        <v>435255</v>
       </c>
       <c r="R129" t="n">
-        <v>6783240</v>
+        <v>6783275</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13409,6 +13408,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13427,10 +13427,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129963839</v>
+        <v>129963709</v>
       </c>
       <c r="B130" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13438,21 +13438,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>435149</v>
+        <v>435050</v>
       </c>
       <c r="R130" t="n">
-        <v>6783386</v>
+        <v>6783376</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13498,11 +13498,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13529,10 +13524,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129963709</v>
+        <v>129963839</v>
       </c>
       <c r="B131" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13540,21 +13535,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13564,10 +13559,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>435050</v>
+        <v>435149</v>
       </c>
       <c r="R131" t="n">
-        <v>6783376</v>
+        <v>6783386</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13600,6 +13595,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13733,7 +13733,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129963702</v>
+        <v>129963699</v>
       </c>
       <c r="B133" t="n">
         <v>79703</v>
@@ -13768,10 +13768,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>435064</v>
+        <v>435081</v>
       </c>
       <c r="R133" t="n">
-        <v>6783239</v>
+        <v>6783223</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13830,10 +13830,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129963851</v>
+        <v>129963683</v>
       </c>
       <c r="B134" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13841,21 +13841,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>434938</v>
+        <v>435093</v>
       </c>
       <c r="R134" t="n">
-        <v>6783327</v>
+        <v>6783192</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13927,7 +13927,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129963699</v>
+        <v>129963700</v>
       </c>
       <c r="B135" t="n">
         <v>79703</v>
@@ -13962,10 +13962,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>435081</v>
+        <v>435068</v>
       </c>
       <c r="R135" t="n">
-        <v>6783223</v>
+        <v>6783233</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129963836</v>
+        <v>129963690</v>
       </c>
       <c r="B136" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14035,21 +14035,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>435073</v>
+        <v>435121</v>
       </c>
       <c r="R136" t="n">
-        <v>6783270</v>
+        <v>6783166</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14095,11 +14095,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14126,7 +14121,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129963700</v>
+        <v>129963702</v>
       </c>
       <c r="B137" t="n">
         <v>79703</v>
@@ -14161,10 +14156,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>435068</v>
+        <v>435064</v>
       </c>
       <c r="R137" t="n">
-        <v>6783233</v>
+        <v>6783239</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14223,10 +14218,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129963690</v>
+        <v>129963828</v>
       </c>
       <c r="B138" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14234,21 +14229,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14258,10 +14253,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>435121</v>
+        <v>435102</v>
       </c>
       <c r="R138" t="n">
-        <v>6783166</v>
+        <v>6783177</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14294,6 +14289,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14320,7 +14320,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129963828</v>
+        <v>129963851</v>
       </c>
       <c r="B139" t="n">
         <v>79084</v>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>435102</v>
+        <v>434938</v>
       </c>
       <c r="R139" t="n">
-        <v>6783177</v>
+        <v>6783327</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14391,11 +14391,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14422,10 +14417,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129963683</v>
+        <v>129963836</v>
       </c>
       <c r="B140" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14433,21 +14428,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14457,10 +14452,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>435093</v>
+        <v>435073</v>
       </c>
       <c r="R140" t="n">
-        <v>6783192</v>
+        <v>6783270</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14493,6 +14488,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50.</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 7913-2025 artfynd.xlsx
+++ b/artfynd/A 7913-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129963742</v>
+        <v>129963682</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434938</v>
+        <v>435075</v>
       </c>
       <c r="R2" t="n">
-        <v>6783317</v>
+        <v>6783207</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129963682</v>
+        <v>129963715</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435075</v>
+        <v>434862</v>
       </c>
       <c r="R3" t="n">
-        <v>6783207</v>
+        <v>6783371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129963715</v>
+        <v>129963697</v>
       </c>
       <c r="B4" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434862</v>
+        <v>435140</v>
       </c>
       <c r="R4" t="n">
-        <v>6783371</v>
+        <v>6783274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +969,7 @@
         <v>129963800</v>
       </c>
       <c r="B5" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129963697</v>
+        <v>129963742</v>
       </c>
       <c r="B6" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435140</v>
+        <v>434938</v>
       </c>
       <c r="R6" t="n">
-        <v>6783274</v>
+        <v>6783317</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,45 +1168,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129963799</v>
+        <v>129963785</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435115</v>
+        <v>435286</v>
       </c>
       <c r="R7" t="n">
-        <v>6783224</v>
+        <v>6783280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,6 +1256,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1265,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129963684</v>
+        <v>129963768</v>
       </c>
       <c r="B8" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1300,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435069</v>
+        <v>435080</v>
       </c>
       <c r="R8" t="n">
-        <v>6783183</v>
+        <v>6783283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129963806</v>
+        <v>129963799</v>
       </c>
       <c r="B9" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434862</v>
+        <v>435115</v>
       </c>
       <c r="R9" t="n">
-        <v>6783373</v>
+        <v>6783224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129963768</v>
+        <v>129963684</v>
       </c>
       <c r="B10" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1494,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435080</v>
+        <v>435069</v>
       </c>
       <c r="R10" t="n">
-        <v>6783283</v>
+        <v>6783183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,54 +1566,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129963785</v>
+        <v>129963806</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>78844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435286</v>
+        <v>434862</v>
       </c>
       <c r="R11" t="n">
-        <v>6783280</v>
+        <v>6783373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,7 +1645,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129963775</v>
+        <v>129963843</v>
       </c>
       <c r="B12" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434969</v>
+        <v>435037</v>
       </c>
       <c r="R12" t="n">
-        <v>6783298</v>
+        <v>6783350</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1734,6 +1734,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1760,10 +1765,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129963760</v>
+        <v>129963838</v>
       </c>
       <c r="B13" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,24 +1776,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
@@ -1798,7 +1806,7 @@
         <v>435131</v>
       </c>
       <c r="R13" t="n">
-        <v>6783264</v>
+        <v>6783363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,12 +1841,18 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1857,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129963774</v>
+        <v>129963775</v>
       </c>
       <c r="B14" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1892,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435002</v>
+        <v>434969</v>
       </c>
       <c r="R14" t="n">
-        <v>6783410</v>
+        <v>6783298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129963778</v>
+        <v>129963760</v>
       </c>
       <c r="B15" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434872</v>
+        <v>435131</v>
       </c>
       <c r="R15" t="n">
-        <v>6783360</v>
+        <v>6783264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129963843</v>
+        <v>129963774</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2062,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2086,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435037</v>
+        <v>435002</v>
       </c>
       <c r="R16" t="n">
-        <v>6783350</v>
+        <v>6783410</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,11 +2136,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2153,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129963838</v>
+        <v>129963778</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2164,37 +2173,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435131</v>
+        <v>434872</v>
       </c>
       <c r="R17" t="n">
-        <v>6783363</v>
+        <v>6783360</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,18 +2235,12 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129963830</v>
+        <v>129963758</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435195</v>
+        <v>435121</v>
       </c>
       <c r="R18" t="n">
-        <v>6783259</v>
+        <v>6783166</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2356,45 +2356,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129963850</v>
+        <v>129963792</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434979</v>
+        <v>435029</v>
       </c>
       <c r="R19" t="n">
-        <v>6783324</v>
+        <v>6783411</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,6 +2444,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2453,45 +2463,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129963849</v>
+        <v>129963784</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434989</v>
+        <v>435269</v>
       </c>
       <c r="R20" t="n">
-        <v>6783322</v>
+        <v>6783269</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,6 +2551,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2550,10 +2570,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129963694</v>
+        <v>129963830</v>
       </c>
       <c r="B21" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,21 +2581,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435287</v>
+        <v>435195</v>
       </c>
       <c r="R21" t="n">
-        <v>6783290</v>
+        <v>6783259</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,10 +2667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129963798</v>
+        <v>129963850</v>
       </c>
       <c r="B22" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2658,21 +2678,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2682,10 +2702,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435226</v>
+        <v>434979</v>
       </c>
       <c r="R22" t="n">
-        <v>6783162</v>
+        <v>6783324</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2744,54 +2764,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129963792</v>
+        <v>129963849</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435029</v>
+        <v>434989</v>
       </c>
       <c r="R23" t="n">
-        <v>6783411</v>
+        <v>6783322</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2832,7 +2843,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2851,54 +2861,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129963784</v>
+        <v>129963694</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435269</v>
+        <v>435287</v>
       </c>
       <c r="R24" t="n">
-        <v>6783269</v>
+        <v>6783290</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2939,7 +2940,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129963758</v>
+        <v>129963798</v>
       </c>
       <c r="B25" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435121</v>
+        <v>435226</v>
       </c>
       <c r="R25" t="n">
-        <v>6783166</v>
+        <v>6783162</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129963714</v>
+        <v>129963739</v>
       </c>
       <c r="B26" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,34 +3066,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434952</v>
+        <v>435244</v>
       </c>
       <c r="R26" t="n">
-        <v>6783307</v>
+        <v>6783276</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129963739</v>
+        <v>129963770</v>
       </c>
       <c r="B27" t="n">
-        <v>57734</v>
+        <v>78845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3163,42 +3171,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435244</v>
+        <v>435151</v>
       </c>
       <c r="R27" t="n">
-        <v>6783276</v>
+        <v>6783386</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129963827</v>
+        <v>129963723</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435224</v>
+        <v>435137</v>
       </c>
       <c r="R28" t="n">
-        <v>6783121</v>
+        <v>6783270</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963848</v>
+        <v>129963827</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434993</v>
+        <v>435224</v>
       </c>
       <c r="R29" t="n">
-        <v>6783317</v>
+        <v>6783121</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,11 +3425,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3456,10 +3451,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963831</v>
+        <v>129963848</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435239</v>
+        <v>434993</v>
       </c>
       <c r="R30" t="n">
-        <v>6783254</v>
+        <v>6783317</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3527,6 +3522,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129963770</v>
+        <v>129963831</v>
       </c>
       <c r="B31" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435151</v>
+        <v>435239</v>
       </c>
       <c r="R31" t="n">
-        <v>6783386</v>
+        <v>6783254</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,10 +3650,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129963723</v>
+        <v>129963714</v>
       </c>
       <c r="B32" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3661,21 +3661,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435137</v>
+        <v>434952</v>
       </c>
       <c r="R32" t="n">
-        <v>6783270</v>
+        <v>6783307</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129963762</v>
+        <v>129963842</v>
       </c>
       <c r="B33" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435102</v>
+        <v>435074</v>
       </c>
       <c r="R33" t="n">
-        <v>6783245</v>
+        <v>6783347</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,6 +3818,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3844,10 +3849,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129963719</v>
+        <v>129963834</v>
       </c>
       <c r="B34" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3860,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435236</v>
+        <v>435136</v>
       </c>
       <c r="R34" t="n">
-        <v>6783256</v>
+        <v>6783253</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,6 +3920,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3941,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129963724</v>
+        <v>129963803</v>
       </c>
       <c r="B35" t="n">
-        <v>79674</v>
+        <v>78844</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3952,21 +3962,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435055</v>
+        <v>435063</v>
       </c>
       <c r="R35" t="n">
-        <v>6783236</v>
+        <v>6783239</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129963767</v>
+        <v>129963762</v>
       </c>
       <c r="B36" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435066</v>
+        <v>435102</v>
       </c>
       <c r="R36" t="n">
-        <v>6783276</v>
+        <v>6783245</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4135,10 +4145,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129963803</v>
+        <v>129963719</v>
       </c>
       <c r="B37" t="n">
-        <v>78841</v>
+        <v>79677</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4146,21 +4156,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4170,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435063</v>
+        <v>435236</v>
       </c>
       <c r="R37" t="n">
-        <v>6783239</v>
+        <v>6783256</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4232,10 +4242,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129963842</v>
+        <v>129963724</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4243,21 +4253,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4267,10 +4277,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435074</v>
+        <v>435055</v>
       </c>
       <c r="R38" t="n">
-        <v>6783347</v>
+        <v>6783236</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4303,11 +4313,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4334,10 +4339,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129963834</v>
+        <v>129963767</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4345,21 +4350,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4374,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435136</v>
+        <v>435066</v>
       </c>
       <c r="R39" t="n">
-        <v>6783253</v>
+        <v>6783276</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4405,11 +4410,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4436,53 +4436,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129963738</v>
+        <v>129963731</v>
       </c>
       <c r="B40" t="n">
-        <v>57734</v>
+        <v>91569</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435231</v>
+        <v>434932</v>
       </c>
       <c r="R40" t="n">
-        <v>6783171</v>
+        <v>6783346</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4523,8 +4515,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4541,10 +4554,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129963743</v>
+        <v>129963854</v>
       </c>
       <c r="B41" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4552,42 +4565,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434936</v>
+        <v>434905</v>
       </c>
       <c r="R41" t="n">
-        <v>6783319</v>
+        <v>6783388</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,10 +4651,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129963737</v>
+        <v>129963705</v>
       </c>
       <c r="B42" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4657,42 +4662,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435238</v>
+        <v>435151</v>
       </c>
       <c r="R42" t="n">
-        <v>6783110</v>
+        <v>6783380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,10 +4748,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129963750</v>
+        <v>129963738</v>
       </c>
       <c r="B43" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4762,34 +4759,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435002</v>
+        <v>435231</v>
       </c>
       <c r="R43" t="n">
-        <v>6783275</v>
+        <v>6783171</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,10 +4853,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129963705</v>
+        <v>129963743</v>
       </c>
       <c r="B44" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4859,34 +4864,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435151</v>
+        <v>434936</v>
       </c>
       <c r="R44" t="n">
-        <v>6783380</v>
+        <v>6783319</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4945,45 +4958,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129963731</v>
+        <v>129963737</v>
       </c>
       <c r="B45" t="n">
-        <v>91566</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434932</v>
+        <v>435238</v>
       </c>
       <c r="R45" t="n">
-        <v>6783346</v>
+        <v>6783110</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5024,29 +5045,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5063,45 +5063,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129963854</v>
+        <v>129963789</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434905</v>
+        <v>435157</v>
       </c>
       <c r="R46" t="n">
-        <v>6783388</v>
+        <v>6783283</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5142,6 +5151,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5160,54 +5170,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129963789</v>
+        <v>129963750</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435157</v>
+        <v>435002</v>
       </c>
       <c r="R47" t="n">
-        <v>6783283</v>
+        <v>6783275</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5248,7 +5249,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>129963804</v>
       </c>
       <c r="B48" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5364,10 +5364,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129963703</v>
+        <v>129963801</v>
       </c>
       <c r="B49" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5375,21 +5375,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435072</v>
+        <v>435140</v>
       </c>
       <c r="R49" t="n">
-        <v>6783251</v>
+        <v>6783274</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5461,45 +5461,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129963801</v>
+        <v>129963858</v>
       </c>
       <c r="B50" t="n">
-        <v>78841</v>
+        <v>8440</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435140</v>
+        <v>434900</v>
       </c>
       <c r="R50" t="n">
-        <v>6783274</v>
+        <v>6783402</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5540,6 +5549,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5558,10 +5568,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129963823</v>
+        <v>129963718</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,21 +5579,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5593,10 +5603,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435065</v>
+        <v>435195</v>
       </c>
       <c r="R51" t="n">
-        <v>6783208</v>
+        <v>6783256</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5655,54 +5665,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129963858</v>
+        <v>129963823</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434900</v>
+        <v>435065</v>
       </c>
       <c r="R52" t="n">
-        <v>6783402</v>
+        <v>6783208</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5743,7 +5744,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129963759</v>
+        <v>129963703</v>
       </c>
       <c r="B53" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435138</v>
+        <v>435072</v>
       </c>
       <c r="R53" t="n">
-        <v>6783290</v>
+        <v>6783251</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5859,10 +5859,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129963718</v>
+        <v>129963759</v>
       </c>
       <c r="B54" t="n">
-        <v>79674</v>
+        <v>78845</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5870,21 +5870,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435195</v>
+        <v>435138</v>
       </c>
       <c r="R54" t="n">
-        <v>6783256</v>
+        <v>6783290</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5956,10 +5956,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129963746</v>
+        <v>129963846</v>
       </c>
       <c r="B55" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,42 +5967,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434861</v>
+        <v>435021</v>
       </c>
       <c r="R55" t="n">
-        <v>6783366</v>
+        <v>6783388</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6061,10 +6053,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129963856</v>
+        <v>129963782</v>
       </c>
       <c r="B56" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6072,21 +6064,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6105,10 +6097,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435075</v>
+        <v>435240</v>
       </c>
       <c r="R56" t="n">
-        <v>6783111</v>
+        <v>6783151</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6168,10 +6160,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129963696</v>
+        <v>129963749</v>
       </c>
       <c r="B57" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6179,21 +6171,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6203,10 +6195,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435135</v>
+        <v>434946</v>
       </c>
       <c r="R57" t="n">
-        <v>6783269</v>
+        <v>6783406</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6265,10 +6257,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129963708</v>
+        <v>129963753</v>
       </c>
       <c r="B58" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6276,21 +6268,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6300,10 +6292,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435013</v>
+        <v>435074</v>
       </c>
       <c r="R58" t="n">
-        <v>6783367</v>
+        <v>6783208</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6362,10 +6354,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129963681</v>
+        <v>129963727</v>
       </c>
       <c r="B59" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6373,21 +6365,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6397,10 +6389,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435046</v>
+        <v>435156</v>
       </c>
       <c r="R59" t="n">
-        <v>6783227</v>
+        <v>6783404</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6459,10 +6451,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129963846</v>
+        <v>129963696</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6470,21 +6462,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6494,10 +6486,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435021</v>
+        <v>435135</v>
       </c>
       <c r="R60" t="n">
-        <v>6783388</v>
+        <v>6783269</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,54 +6548,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129963782</v>
+        <v>129963708</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435240</v>
+        <v>435013</v>
       </c>
       <c r="R61" t="n">
-        <v>6783151</v>
+        <v>6783367</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6644,7 +6627,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6663,10 +6645,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129963749</v>
+        <v>129963681</v>
       </c>
       <c r="B62" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6674,21 +6656,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6698,10 +6680,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434946</v>
+        <v>435046</v>
       </c>
       <c r="R62" t="n">
-        <v>6783406</v>
+        <v>6783227</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6760,10 +6742,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129963763</v>
+        <v>129963746</v>
       </c>
       <c r="B63" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6771,34 +6753,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435052</v>
+        <v>434861</v>
       </c>
       <c r="R63" t="n">
-        <v>6783227</v>
+        <v>6783366</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6857,45 +6847,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129963720</v>
+        <v>129963856</v>
       </c>
       <c r="B64" t="n">
-        <v>79674</v>
+        <v>5177</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435263</v>
+        <v>435075</v>
       </c>
       <c r="R64" t="n">
-        <v>6783286</v>
+        <v>6783111</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6936,6 +6935,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6954,10 +6954,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129963753</v>
+        <v>129963763</v>
       </c>
       <c r="B65" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>435074</v>
+        <v>435052</v>
       </c>
       <c r="R65" t="n">
-        <v>6783208</v>
+        <v>6783227</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7051,10 +7051,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129963727</v>
+        <v>129963720</v>
       </c>
       <c r="B66" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435156</v>
+        <v>435263</v>
       </c>
       <c r="R66" t="n">
-        <v>6783404</v>
+        <v>6783286</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7148,53 +7148,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129963748</v>
+        <v>129963837</v>
       </c>
       <c r="B67" t="n">
-        <v>56930</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435072</v>
+        <v>435094</v>
       </c>
       <c r="R67" t="n">
-        <v>6783347</v>
+        <v>6783352</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7253,10 +7245,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129963701</v>
+        <v>129963688</v>
       </c>
       <c r="B68" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7288,10 +7280,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435051</v>
+        <v>435226</v>
       </c>
       <c r="R68" t="n">
-        <v>6783226</v>
+        <v>6783162</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7350,45 +7342,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129963707</v>
+        <v>129963748</v>
       </c>
       <c r="B69" t="n">
-        <v>79703</v>
+        <v>56933</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435035</v>
+        <v>435072</v>
       </c>
       <c r="R69" t="n">
-        <v>6783349</v>
+        <v>6783347</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7447,10 +7447,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129963688</v>
+        <v>129963735</v>
       </c>
       <c r="B70" t="n">
-        <v>79703</v>
+        <v>57898</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7458,34 +7458,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435226</v>
+        <v>435028</v>
       </c>
       <c r="R70" t="n">
-        <v>6783162</v>
+        <v>6783350</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7544,10 +7552,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129963837</v>
+        <v>129963761</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7555,21 +7563,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7579,10 +7587,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435094</v>
+        <v>435140</v>
       </c>
       <c r="R71" t="n">
-        <v>6783352</v>
+        <v>6783272</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7641,10 +7649,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129963735</v>
+        <v>129963764</v>
       </c>
       <c r="B72" t="n">
-        <v>57895</v>
+        <v>78845</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7652,42 +7660,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435028</v>
+        <v>435059</v>
       </c>
       <c r="R72" t="n">
-        <v>6783350</v>
+        <v>6783248</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7746,10 +7746,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129963761</v>
+        <v>129963728</v>
       </c>
       <c r="B73" t="n">
-        <v>78842</v>
+        <v>79677</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7757,21 +7757,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435140</v>
+        <v>435152</v>
       </c>
       <c r="R73" t="n">
-        <v>6783272</v>
+        <v>6783393</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129963764</v>
+        <v>129963701</v>
       </c>
       <c r="B74" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7854,21 +7854,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7878,10 +7878,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435059</v>
+        <v>435051</v>
       </c>
       <c r="R74" t="n">
-        <v>6783248</v>
+        <v>6783226</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7940,10 +7940,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129963728</v>
+        <v>129963707</v>
       </c>
       <c r="B75" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7951,21 +7951,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435152</v>
+        <v>435035</v>
       </c>
       <c r="R75" t="n">
-        <v>6783393</v>
+        <v>6783349</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8037,43 +8037,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129963781</v>
+        <v>129963853</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8081,10 +8075,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>435073</v>
+        <v>434958</v>
       </c>
       <c r="R76" t="n">
-        <v>6783120</v>
+        <v>6783365</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8144,10 +8138,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129963717</v>
+        <v>129963820</v>
       </c>
       <c r="B77" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8155,21 +8149,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8179,10 +8173,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435121</v>
+        <v>435070</v>
       </c>
       <c r="R77" t="n">
-        <v>6783164</v>
+        <v>6783207</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8241,10 +8235,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129963716</v>
+        <v>129963689</v>
       </c>
       <c r="B78" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8252,21 +8246,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8276,10 +8270,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435184</v>
+        <v>435225</v>
       </c>
       <c r="R78" t="n">
-        <v>6783109</v>
+        <v>6783144</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8338,10 +8332,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129963689</v>
+        <v>129963704</v>
       </c>
       <c r="B79" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8373,10 +8367,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435225</v>
+        <v>435073</v>
       </c>
       <c r="R79" t="n">
-        <v>6783144</v>
+        <v>6783319</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8435,35 +8429,44 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129963704</v>
+        <v>129963781</v>
       </c>
       <c r="B80" t="n">
-        <v>79703</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
@@ -8473,7 +8476,7 @@
         <v>435073</v>
       </c>
       <c r="R80" t="n">
-        <v>6783319</v>
+        <v>6783120</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8514,6 +8517,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8532,10 +8536,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129963853</v>
+        <v>129963717</v>
       </c>
       <c r="B81" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8543,37 +8547,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434958</v>
+        <v>435121</v>
       </c>
       <c r="R81" t="n">
-        <v>6783365</v>
+        <v>6783164</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8614,7 +8615,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8633,10 +8633,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129963820</v>
+        <v>129963716</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8644,21 +8644,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435070</v>
+        <v>435184</v>
       </c>
       <c r="R82" t="n">
-        <v>6783207</v>
+        <v>6783109</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8730,10 +8730,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129963829</v>
+        <v>129963847</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435142</v>
+        <v>435018</v>
       </c>
       <c r="R83" t="n">
-        <v>6783234</v>
+        <v>6783344</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8801,11 +8801,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8832,10 +8827,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129963765</v>
+        <v>129963829</v>
       </c>
       <c r="B84" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8843,21 +8838,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8867,10 +8862,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435080</v>
+        <v>435142</v>
       </c>
       <c r="R84" t="n">
-        <v>6783254</v>
+        <v>6783234</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8903,6 +8898,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8932,7 +8932,7 @@
         <v>129963713</v>
       </c>
       <c r="B85" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9026,45 +9026,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129963847</v>
+        <v>129963779</v>
       </c>
       <c r="B86" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435018</v>
+        <v>434963</v>
       </c>
       <c r="R86" t="n">
-        <v>6783344</v>
+        <v>6783366</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9105,6 +9114,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9123,54 +9133,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129963779</v>
+        <v>129963765</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434963</v>
+        <v>435080</v>
       </c>
       <c r="R87" t="n">
-        <v>6783366</v>
+        <v>6783254</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9211,7 +9212,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9230,54 +9230,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129963794</v>
+        <v>129963825</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434903</v>
+        <v>435247</v>
       </c>
       <c r="R88" t="n">
-        <v>6783388</v>
+        <v>6783126</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9318,7 +9309,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9337,10 +9327,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129963825</v>
+        <v>129963832</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9372,10 +9362,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>435247</v>
+        <v>435150</v>
       </c>
       <c r="R89" t="n">
-        <v>6783126</v>
+        <v>6783272</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9434,10 +9424,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129963832</v>
+        <v>129963710</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9445,21 +9435,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9469,10 +9459,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>435150</v>
+        <v>435047</v>
       </c>
       <c r="R90" t="n">
-        <v>6783272</v>
+        <v>6783384</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9531,10 +9521,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129963710</v>
+        <v>129963691</v>
       </c>
       <c r="B91" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9566,10 +9556,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>435047</v>
+        <v>435115</v>
       </c>
       <c r="R91" t="n">
-        <v>6783384</v>
+        <v>6783224</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9628,10 +9618,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129963691</v>
+        <v>129963692</v>
       </c>
       <c r="B92" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9663,10 +9653,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435115</v>
+        <v>435238</v>
       </c>
       <c r="R92" t="n">
-        <v>6783224</v>
+        <v>6783256</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9725,45 +9715,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129963692</v>
+        <v>129963794</v>
       </c>
       <c r="B93" t="n">
-        <v>79703</v>
+        <v>8451</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>435238</v>
+        <v>434903</v>
       </c>
       <c r="R93" t="n">
-        <v>6783256</v>
+        <v>6783388</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9804,6 +9803,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>129963686</v>
       </c>
       <c r="B94" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9919,10 +9919,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129963711</v>
+        <v>129963680</v>
       </c>
       <c r="B95" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>435000</v>
+        <v>434999</v>
       </c>
       <c r="R95" t="n">
-        <v>6783432</v>
+        <v>6783278</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10016,10 +10016,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129963680</v>
+        <v>129963711</v>
       </c>
       <c r="B96" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>434999</v>
+        <v>435000</v>
       </c>
       <c r="R96" t="n">
-        <v>6783278</v>
+        <v>6783432</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10116,7 +10116,7 @@
         <v>129963802</v>
       </c>
       <c r="B97" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129963826</v>
+        <v>129963757</v>
       </c>
       <c r="B98" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>435250</v>
+        <v>435226</v>
       </c>
       <c r="R98" t="n">
-        <v>6783158</v>
+        <v>6783162</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10307,10 +10307,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129963745</v>
+        <v>129963777</v>
       </c>
       <c r="B99" t="n">
-        <v>57734</v>
+        <v>78845</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10318,42 +10318,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434942</v>
+        <v>434863</v>
       </c>
       <c r="R99" t="n">
-        <v>6783348</v>
+        <v>6783373</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10412,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129963744</v>
+        <v>129963826</v>
       </c>
       <c r="B100" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10423,42 +10415,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434931</v>
+        <v>435250</v>
       </c>
       <c r="R100" t="n">
-        <v>6783336</v>
+        <v>6783158</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10517,10 +10501,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129963757</v>
+        <v>129963745</v>
       </c>
       <c r="B101" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10528,34 +10512,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>435226</v>
+        <v>434942</v>
       </c>
       <c r="R101" t="n">
-        <v>6783162</v>
+        <v>6783348</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10614,10 +10606,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129963777</v>
+        <v>129963744</v>
       </c>
       <c r="B102" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10625,34 +10617,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434863</v>
+        <v>434931</v>
       </c>
       <c r="R102" t="n">
-        <v>6783373</v>
+        <v>6783336</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10711,10 +10711,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129963687</v>
+        <v>129963821</v>
       </c>
       <c r="B103" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10722,21 +10722,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>435243</v>
+        <v>435042</v>
       </c>
       <c r="R103" t="n">
-        <v>6783165</v>
+        <v>6783226</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129963712</v>
+        <v>129963687</v>
       </c>
       <c r="B104" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434998</v>
+        <v>435243</v>
       </c>
       <c r="R104" t="n">
-        <v>6783407</v>
+        <v>6783165</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10905,10 +10905,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129963821</v>
+        <v>129963712</v>
       </c>
       <c r="B105" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10916,21 +10916,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>435042</v>
+        <v>434998</v>
       </c>
       <c r="R105" t="n">
-        <v>6783226</v>
+        <v>6783407</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11005,7 +11005,7 @@
         <v>129963791</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>129963752</v>
       </c>
       <c r="B107" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>129963754</v>
       </c>
       <c r="B108" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>129963747</v>
       </c>
       <c r="B109" t="n">
-        <v>56310</v>
+        <v>56313</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11408,10 +11408,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129963772</v>
+        <v>129963835</v>
       </c>
       <c r="B110" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11419,21 +11419,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>435050</v>
+        <v>435082</v>
       </c>
       <c r="R110" t="n">
-        <v>6783382</v>
+        <v>6783221</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11479,6 +11479,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11505,10 +11510,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129963835</v>
+        <v>129963772</v>
       </c>
       <c r="B111" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11516,21 +11521,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11540,10 +11545,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>435082</v>
+        <v>435050</v>
       </c>
       <c r="R111" t="n">
-        <v>6783221</v>
+        <v>6783382</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11576,11 +11581,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11610,7 +11610,7 @@
         <v>129963793</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11714,10 +11714,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129963706</v>
+        <v>129963693</v>
       </c>
       <c r="B113" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>435067</v>
+        <v>435260</v>
       </c>
       <c r="R113" t="n">
-        <v>6783353</v>
+        <v>6783290</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11811,10 +11811,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129963693</v>
+        <v>129963698</v>
       </c>
       <c r="B114" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11846,10 +11846,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>435260</v>
+        <v>435103</v>
       </c>
       <c r="R114" t="n">
-        <v>6783290</v>
+        <v>6783246</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11908,45 +11908,54 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129963698</v>
+        <v>129963790</v>
       </c>
       <c r="B115" t="n">
-        <v>79703</v>
+        <v>8451</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>435103</v>
+        <v>435100</v>
       </c>
       <c r="R115" t="n">
-        <v>6783246</v>
+        <v>6783252</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11987,6 +11996,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12008,7 +12018,7 @@
         <v>129963852</v>
       </c>
       <c r="B116" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12105,7 +12115,7 @@
         <v>129963844</v>
       </c>
       <c r="B117" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12204,54 +12214,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129963790</v>
+        <v>129963706</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435100</v>
+        <v>435067</v>
       </c>
       <c r="R118" t="n">
-        <v>6783252</v>
+        <v>6783353</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12292,7 +12293,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12314,7 +12314,7 @@
         <v>129963740</v>
       </c>
       <c r="B119" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12416,54 +12416,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129963780</v>
+        <v>129963845</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435085</v>
+        <v>435002</v>
       </c>
       <c r="R120" t="n">
-        <v>6783160</v>
+        <v>6783412</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12504,7 +12495,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12523,10 +12513,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129963741</v>
+        <v>129963805</v>
       </c>
       <c r="B121" t="n">
-        <v>57734</v>
+        <v>78844</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12534,42 +12524,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435038</v>
+        <v>435113</v>
       </c>
       <c r="R121" t="n">
-        <v>6783388</v>
+        <v>6783386</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12628,10 +12610,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129963805</v>
+        <v>129963741</v>
       </c>
       <c r="B122" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12639,34 +12621,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>435113</v>
+        <v>435038</v>
       </c>
       <c r="R122" t="n">
-        <v>6783386</v>
+        <v>6783388</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12725,45 +12715,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129963845</v>
+        <v>129963780</v>
       </c>
       <c r="B123" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>435002</v>
+        <v>435085</v>
       </c>
       <c r="R123" t="n">
-        <v>6783412</v>
+        <v>6783160</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12804,6 +12803,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12825,7 +12825,7 @@
         <v>129963751</v>
       </c>
       <c r="B124" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>129963722</v>
       </c>
       <c r="B125" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>129963822</v>
       </c>
       <c r="B126" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>129963841</v>
       </c>
       <c r="B127" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13215,40 +13215,41 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129963733</v>
+        <v>129963783</v>
       </c>
       <c r="B128" t="n">
-        <v>57895</v>
+        <v>8451</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -13258,10 +13259,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>435055</v>
+        <v>435255</v>
       </c>
       <c r="R128" t="n">
-        <v>6783240</v>
+        <v>6783275</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13302,6 +13303,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13320,41 +13322,40 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129963783</v>
+        <v>129963733</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>57898</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -13364,10 +13365,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435255</v>
+        <v>435055</v>
       </c>
       <c r="R129" t="n">
-        <v>6783275</v>
+        <v>6783240</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13408,7 +13409,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13430,7 +13430,7 @@
         <v>129963709</v>
       </c>
       <c r="B130" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>129963839</v>
       </c>
       <c r="B131" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>129963787</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129963699</v>
+        <v>129963851</v>
       </c>
       <c r="B133" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13744,21 +13744,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13768,10 +13768,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>435081</v>
+        <v>434938</v>
       </c>
       <c r="R133" t="n">
-        <v>6783223</v>
+        <v>6783327</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13830,10 +13830,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129963683</v>
+        <v>129963836</v>
       </c>
       <c r="B134" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13841,21 +13841,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>435093</v>
+        <v>435073</v>
       </c>
       <c r="R134" t="n">
-        <v>6783192</v>
+        <v>6783270</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13901,6 +13901,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13927,10 +13932,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129963700</v>
+        <v>129963683</v>
       </c>
       <c r="B135" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13962,10 +13967,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>435068</v>
+        <v>435093</v>
       </c>
       <c r="R135" t="n">
-        <v>6783233</v>
+        <v>6783192</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14024,10 +14029,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129963690</v>
+        <v>129963699</v>
       </c>
       <c r="B136" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14059,10 +14064,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>435121</v>
+        <v>435081</v>
       </c>
       <c r="R136" t="n">
-        <v>6783166</v>
+        <v>6783223</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14124,7 +14129,7 @@
         <v>129963702</v>
       </c>
       <c r="B137" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14221,7 +14226,7 @@
         <v>129963828</v>
       </c>
       <c r="B138" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14320,10 +14325,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129963851</v>
+        <v>129963725</v>
       </c>
       <c r="B139" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14331,21 +14336,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14355,10 +14360,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>434938</v>
+        <v>435062</v>
       </c>
       <c r="R139" t="n">
-        <v>6783327</v>
+        <v>6783268</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14417,10 +14422,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129963836</v>
+        <v>129963700</v>
       </c>
       <c r="B140" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14428,21 +14433,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14452,10 +14457,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>435073</v>
+        <v>435068</v>
       </c>
       <c r="R140" t="n">
-        <v>6783270</v>
+        <v>6783233</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14488,11 +14493,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14519,10 +14519,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129963756</v>
+        <v>129963690</v>
       </c>
       <c r="B141" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14530,21 +14530,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14554,10 +14554,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>435087</v>
+        <v>435121</v>
       </c>
       <c r="R141" t="n">
-        <v>6783099</v>
+        <v>6783166</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14616,10 +14616,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129963725</v>
+        <v>129963756</v>
       </c>
       <c r="B142" t="n">
-        <v>79674</v>
+        <v>78845</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14627,21 +14627,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14651,10 +14651,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>435062</v>
+        <v>435087</v>
       </c>
       <c r="R142" t="n">
-        <v>6783268</v>
+        <v>6783099</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14716,7 +14716,7 @@
         <v>129963769</v>
       </c>
       <c r="B143" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 7913-2025 artfynd.xlsx
+++ b/artfynd/A 7913-2025 artfynd.xlsx
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129963758</v>
+        <v>129963830</v>
       </c>
       <c r="B18" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435121</v>
+        <v>435195</v>
       </c>
       <c r="R18" t="n">
-        <v>6783166</v>
+        <v>6783259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2356,54 +2356,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129963792</v>
+        <v>129963850</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435029</v>
+        <v>434979</v>
       </c>
       <c r="R19" t="n">
-        <v>6783411</v>
+        <v>6783324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,7 +2435,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2463,54 +2453,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129963784</v>
+        <v>129963849</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435269</v>
+        <v>434989</v>
       </c>
       <c r="R20" t="n">
-        <v>6783269</v>
+        <v>6783322</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,7 +2532,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2570,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129963830</v>
+        <v>129963694</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2581,21 +2561,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2605,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435195</v>
+        <v>435287</v>
       </c>
       <c r="R21" t="n">
-        <v>6783259</v>
+        <v>6783290</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2667,10 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129963850</v>
+        <v>129963798</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2678,21 +2658,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2702,10 +2682,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434979</v>
+        <v>435226</v>
       </c>
       <c r="R22" t="n">
-        <v>6783324</v>
+        <v>6783162</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2764,10 +2744,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129963849</v>
+        <v>129963758</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2775,21 +2755,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2799,10 +2779,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434989</v>
+        <v>435121</v>
       </c>
       <c r="R23" t="n">
-        <v>6783322</v>
+        <v>6783166</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2861,45 +2841,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129963694</v>
+        <v>129963792</v>
       </c>
       <c r="B24" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435287</v>
+        <v>435029</v>
       </c>
       <c r="R24" t="n">
-        <v>6783290</v>
+        <v>6783411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2940,6 +2929,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2958,45 +2948,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129963798</v>
+        <v>129963784</v>
       </c>
       <c r="B25" t="n">
-        <v>78844</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435226</v>
+        <v>435269</v>
       </c>
       <c r="R25" t="n">
-        <v>6783162</v>
+        <v>6783269</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3037,6 +3036,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129963739</v>
+        <v>129963827</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,42 +3066,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435244</v>
+        <v>435224</v>
       </c>
       <c r="R26" t="n">
-        <v>6783276</v>
+        <v>6783121</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3160,10 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129963770</v>
+        <v>129963848</v>
       </c>
       <c r="B27" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3171,21 +3163,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3187,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435151</v>
+        <v>434993</v>
       </c>
       <c r="R27" t="n">
-        <v>6783386</v>
+        <v>6783317</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3231,6 +3223,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3257,10 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129963723</v>
+        <v>129963831</v>
       </c>
       <c r="B28" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,21 +3265,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3289,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435137</v>
+        <v>435239</v>
       </c>
       <c r="R28" t="n">
-        <v>6783270</v>
+        <v>6783254</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3354,10 +3351,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963827</v>
+        <v>129963714</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3362,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3386,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435224</v>
+        <v>434952</v>
       </c>
       <c r="R29" t="n">
-        <v>6783121</v>
+        <v>6783307</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3451,10 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963848</v>
+        <v>129963770</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3459,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3483,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434993</v>
+        <v>435151</v>
       </c>
       <c r="R30" t="n">
-        <v>6783317</v>
+        <v>6783386</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3522,11 +3519,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,10 +3545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129963831</v>
+        <v>129963723</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3556,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3580,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435239</v>
+        <v>435137</v>
       </c>
       <c r="R31" t="n">
-        <v>6783254</v>
+        <v>6783270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129963714</v>
+        <v>129963739</v>
       </c>
       <c r="B32" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3661,34 +3653,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434952</v>
+        <v>435244</v>
       </c>
       <c r="R32" t="n">
-        <v>6783307</v>
+        <v>6783276</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129963731</v>
+        <v>129963854</v>
       </c>
       <c r="B40" t="n">
-        <v>91569</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434932</v>
+        <v>434905</v>
       </c>
       <c r="R40" t="n">
-        <v>6783346</v>
+        <v>6783388</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4515,29 +4515,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4554,10 +4533,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129963854</v>
+        <v>129963738</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4565,34 +4544,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434905</v>
+        <v>435231</v>
       </c>
       <c r="R41" t="n">
-        <v>6783388</v>
+        <v>6783171</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4651,10 +4638,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129963705</v>
+        <v>129963743</v>
       </c>
       <c r="B42" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4662,34 +4649,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435151</v>
+        <v>434936</v>
       </c>
       <c r="R42" t="n">
-        <v>6783380</v>
+        <v>6783319</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4748,7 +4743,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129963738</v>
+        <v>129963737</v>
       </c>
       <c r="B43" t="n">
         <v>57737</v>
@@ -4781,7 +4776,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4791,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435231</v>
+        <v>435238</v>
       </c>
       <c r="R43" t="n">
-        <v>6783171</v>
+        <v>6783110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,53 +4848,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129963743</v>
+        <v>129963731</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>91569</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434936</v>
+        <v>434932</v>
       </c>
       <c r="R44" t="n">
-        <v>6783319</v>
+        <v>6783346</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4940,8 +4927,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4958,10 +4966,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129963737</v>
+        <v>129963705</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4969,42 +4977,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435238</v>
+        <v>435151</v>
       </c>
       <c r="R45" t="n">
-        <v>6783110</v>
+        <v>6783380</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -11714,10 +11714,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129963693</v>
+        <v>129963852</v>
       </c>
       <c r="B113" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11725,21 +11725,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>435260</v>
+        <v>434938</v>
       </c>
       <c r="R113" t="n">
-        <v>6783290</v>
+        <v>6783373</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11811,10 +11811,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129963698</v>
+        <v>129963844</v>
       </c>
       <c r="B114" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11822,21 +11822,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11846,10 +11846,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>435103</v>
+        <v>435038</v>
       </c>
       <c r="R114" t="n">
-        <v>6783246</v>
+        <v>6783417</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11882,6 +11882,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11908,54 +11913,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129963790</v>
+        <v>129963706</v>
       </c>
       <c r="B115" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>435100</v>
+        <v>435067</v>
       </c>
       <c r="R115" t="n">
-        <v>6783252</v>
+        <v>6783353</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11996,7 +11992,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12015,10 +12010,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129963852</v>
+        <v>129963740</v>
       </c>
       <c r="B116" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12026,34 +12021,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434938</v>
+        <v>435041</v>
       </c>
       <c r="R116" t="n">
-        <v>6783373</v>
+        <v>6783374</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12112,10 +12115,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129963844</v>
+        <v>129963693</v>
       </c>
       <c r="B117" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12123,21 +12126,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12147,10 +12150,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>435038</v>
+        <v>435260</v>
       </c>
       <c r="R117" t="n">
-        <v>6783417</v>
+        <v>6783290</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12183,11 +12186,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12214,7 +12212,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129963706</v>
+        <v>129963698</v>
       </c>
       <c r="B118" t="n">
         <v>79706</v>
@@ -12249,10 +12247,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435067</v>
+        <v>435103</v>
       </c>
       <c r="R118" t="n">
-        <v>6783353</v>
+        <v>6783246</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12311,40 +12309,41 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129963740</v>
+        <v>129963790</v>
       </c>
       <c r="B119" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -12354,10 +12353,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435041</v>
+        <v>435100</v>
       </c>
       <c r="R119" t="n">
-        <v>6783374</v>
+        <v>6783252</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12398,6 +12397,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129963845</v>
+        <v>129963741</v>
       </c>
       <c r="B120" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12427,34 +12427,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435002</v>
+        <v>435038</v>
       </c>
       <c r="R120" t="n">
-        <v>6783412</v>
+        <v>6783388</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12513,10 +12521,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129963805</v>
+        <v>129963845</v>
       </c>
       <c r="B121" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12524,21 +12532,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12548,10 +12556,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435113</v>
+        <v>435002</v>
       </c>
       <c r="R121" t="n">
-        <v>6783386</v>
+        <v>6783412</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12610,10 +12618,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129963741</v>
+        <v>129963805</v>
       </c>
       <c r="B122" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12621,42 +12629,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>435038</v>
+        <v>435113</v>
       </c>
       <c r="R122" t="n">
-        <v>6783388</v>
+        <v>6783386</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13427,10 +13427,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129963709</v>
+        <v>129963839</v>
       </c>
       <c r="B130" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13438,21 +13438,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>435050</v>
+        <v>435149</v>
       </c>
       <c r="R130" t="n">
-        <v>6783376</v>
+        <v>6783386</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13498,6 +13498,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13524,10 +13529,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129963839</v>
+        <v>129963709</v>
       </c>
       <c r="B131" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13535,21 +13540,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13559,10 +13564,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>435149</v>
+        <v>435050</v>
       </c>
       <c r="R131" t="n">
-        <v>6783386</v>
+        <v>6783376</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13595,11 +13600,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 7913-2025 artfynd.xlsx
+++ b/artfynd/A 7913-2025 artfynd.xlsx
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129963842</v>
+        <v>129963803</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435074</v>
+        <v>435063</v>
       </c>
       <c r="R33" t="n">
-        <v>6783347</v>
+        <v>6783239</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,11 +3818,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3849,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129963834</v>
+        <v>129963762</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3860,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435136</v>
+        <v>435102</v>
       </c>
       <c r="R34" t="n">
-        <v>6783253</v>
+        <v>6783245</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3920,11 +3915,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,10 +3941,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129963803</v>
+        <v>129963719</v>
       </c>
       <c r="B35" t="n">
-        <v>78844</v>
+        <v>79677</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3962,21 +3952,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435063</v>
+        <v>435236</v>
       </c>
       <c r="R35" t="n">
-        <v>6783239</v>
+        <v>6783256</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4048,10 +4038,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129963762</v>
+        <v>129963724</v>
       </c>
       <c r="B36" t="n">
-        <v>78845</v>
+        <v>79677</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,21 +4049,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435102</v>
+        <v>435055</v>
       </c>
       <c r="R36" t="n">
-        <v>6783245</v>
+        <v>6783236</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4145,10 +4135,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129963719</v>
+        <v>129963767</v>
       </c>
       <c r="B37" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4156,21 +4146,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4180,10 +4170,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435236</v>
+        <v>435066</v>
       </c>
       <c r="R37" t="n">
-        <v>6783256</v>
+        <v>6783276</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4242,10 +4232,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129963724</v>
+        <v>129963842</v>
       </c>
       <c r="B38" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4253,21 +4243,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4277,10 +4267,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435055</v>
+        <v>435074</v>
       </c>
       <c r="R38" t="n">
-        <v>6783236</v>
+        <v>6783347</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4313,6 +4303,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4339,10 +4334,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129963767</v>
+        <v>129963834</v>
       </c>
       <c r="B39" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4350,21 +4345,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435066</v>
+        <v>435136</v>
       </c>
       <c r="R39" t="n">
-        <v>6783276</v>
+        <v>6783253</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4410,6 +4405,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129963854</v>
+        <v>129963731</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>91569</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434905</v>
+        <v>434932</v>
       </c>
       <c r="R40" t="n">
-        <v>6783388</v>
+        <v>6783346</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4515,8 +4515,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4533,10 +4554,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129963738</v>
+        <v>129963854</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4544,42 +4565,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435231</v>
+        <v>434905</v>
       </c>
       <c r="R41" t="n">
-        <v>6783171</v>
+        <v>6783388</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4638,10 +4651,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129963743</v>
+        <v>129963705</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4649,42 +4662,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434936</v>
+        <v>435151</v>
       </c>
       <c r="R42" t="n">
-        <v>6783319</v>
+        <v>6783380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,7 +4748,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129963737</v>
+        <v>129963738</v>
       </c>
       <c r="B43" t="n">
         <v>57737</v>
@@ -4776,7 +4781,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4786,10 +4791,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435238</v>
+        <v>435231</v>
       </c>
       <c r="R43" t="n">
-        <v>6783110</v>
+        <v>6783171</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,45 +4853,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129963731</v>
+        <v>129963743</v>
       </c>
       <c r="B44" t="n">
-        <v>91569</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434932</v>
+        <v>434936</v>
       </c>
       <c r="R44" t="n">
-        <v>6783346</v>
+        <v>6783319</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4927,29 +4940,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4966,10 +4958,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129963705</v>
+        <v>129963737</v>
       </c>
       <c r="B45" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4977,34 +4969,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435151</v>
+        <v>435238</v>
       </c>
       <c r="R45" t="n">
-        <v>6783380</v>
+        <v>6783110</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5063,54 +5063,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129963789</v>
+        <v>129963750</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>78845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435157</v>
+        <v>435002</v>
       </c>
       <c r="R46" t="n">
-        <v>6783283</v>
+        <v>6783275</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5151,7 +5142,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5170,45 +5160,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129963750</v>
+        <v>129963789</v>
       </c>
       <c r="B47" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435002</v>
+        <v>435157</v>
       </c>
       <c r="R47" t="n">
-        <v>6783275</v>
+        <v>6783283</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5249,6 +5248,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5956,10 +5956,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129963846</v>
+        <v>129963763</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435021</v>
+        <v>435052</v>
       </c>
       <c r="R55" t="n">
-        <v>6783388</v>
+        <v>6783227</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6053,54 +6053,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129963782</v>
+        <v>129963696</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435240</v>
+        <v>435135</v>
       </c>
       <c r="R56" t="n">
-        <v>6783151</v>
+        <v>6783269</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6141,7 +6132,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6160,10 +6150,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129963749</v>
+        <v>129963708</v>
       </c>
       <c r="B57" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6171,21 +6161,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6195,10 +6185,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434946</v>
+        <v>435013</v>
       </c>
       <c r="R57" t="n">
-        <v>6783406</v>
+        <v>6783367</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6257,10 +6247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129963753</v>
+        <v>129963681</v>
       </c>
       <c r="B58" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6268,21 +6258,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6292,10 +6282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435074</v>
+        <v>435046</v>
       </c>
       <c r="R58" t="n">
-        <v>6783208</v>
+        <v>6783227</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6354,10 +6344,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129963727</v>
+        <v>129963846</v>
       </c>
       <c r="B59" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6365,21 +6355,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6389,10 +6379,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435156</v>
+        <v>435021</v>
       </c>
       <c r="R59" t="n">
-        <v>6783404</v>
+        <v>6783388</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6451,10 +6441,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129963696</v>
+        <v>129963746</v>
       </c>
       <c r="B60" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6462,34 +6452,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435135</v>
+        <v>434861</v>
       </c>
       <c r="R60" t="n">
-        <v>6783269</v>
+        <v>6783366</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6548,45 +6546,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129963708</v>
+        <v>129963856</v>
       </c>
       <c r="B61" t="n">
-        <v>79706</v>
+        <v>5177</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435013</v>
+        <v>435075</v>
       </c>
       <c r="R61" t="n">
-        <v>6783367</v>
+        <v>6783111</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6627,6 +6634,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6645,45 +6653,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129963681</v>
+        <v>129963782</v>
       </c>
       <c r="B62" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435046</v>
+        <v>435240</v>
       </c>
       <c r="R62" t="n">
-        <v>6783227</v>
+        <v>6783151</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6724,6 +6741,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6742,10 +6760,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129963746</v>
+        <v>129963749</v>
       </c>
       <c r="B63" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6753,42 +6771,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434861</v>
+        <v>434946</v>
       </c>
       <c r="R63" t="n">
-        <v>6783366</v>
+        <v>6783406</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6847,54 +6857,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129963856</v>
+        <v>129963720</v>
       </c>
       <c r="B64" t="n">
-        <v>5177</v>
+        <v>79677</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435075</v>
+        <v>435263</v>
       </c>
       <c r="R64" t="n">
-        <v>6783111</v>
+        <v>6783286</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6935,7 +6936,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129963763</v>
+        <v>129963753</v>
       </c>
       <c r="B65" t="n">
         <v>78845</v>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>435052</v>
+        <v>435074</v>
       </c>
       <c r="R65" t="n">
-        <v>6783227</v>
+        <v>6783208</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7051,7 +7051,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129963720</v>
+        <v>129963727</v>
       </c>
       <c r="B66" t="n">
         <v>79677</v>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435263</v>
+        <v>435156</v>
       </c>
       <c r="R66" t="n">
-        <v>6783286</v>
+        <v>6783404</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7148,10 +7148,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129963837</v>
+        <v>129963735</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>57898</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7159,34 +7159,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435094</v>
+        <v>435028</v>
       </c>
       <c r="R67" t="n">
-        <v>6783352</v>
+        <v>6783350</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7245,10 +7253,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129963688</v>
+        <v>129963761</v>
       </c>
       <c r="B68" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7256,21 +7264,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7280,10 +7288,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435226</v>
+        <v>435140</v>
       </c>
       <c r="R68" t="n">
-        <v>6783162</v>
+        <v>6783272</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,53 +7350,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129963748</v>
+        <v>129963764</v>
       </c>
       <c r="B69" t="n">
-        <v>56933</v>
+        <v>78845</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435072</v>
+        <v>435059</v>
       </c>
       <c r="R69" t="n">
-        <v>6783347</v>
+        <v>6783248</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7447,10 +7447,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129963735</v>
+        <v>129963728</v>
       </c>
       <c r="B70" t="n">
-        <v>57898</v>
+        <v>79677</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7458,42 +7458,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435028</v>
+        <v>435152</v>
       </c>
       <c r="R70" t="n">
-        <v>6783350</v>
+        <v>6783393</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7552,10 +7544,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129963761</v>
+        <v>129963701</v>
       </c>
       <c r="B71" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7563,21 +7555,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7587,10 +7579,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435140</v>
+        <v>435051</v>
       </c>
       <c r="R71" t="n">
-        <v>6783272</v>
+        <v>6783226</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7649,10 +7641,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129963764</v>
+        <v>129963688</v>
       </c>
       <c r="B72" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7660,21 +7652,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7684,10 +7676,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435059</v>
+        <v>435226</v>
       </c>
       <c r="R72" t="n">
-        <v>6783248</v>
+        <v>6783162</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7746,10 +7738,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129963728</v>
+        <v>129963837</v>
       </c>
       <c r="B73" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7757,21 +7749,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7781,10 +7773,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435152</v>
+        <v>435094</v>
       </c>
       <c r="R73" t="n">
-        <v>6783393</v>
+        <v>6783352</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7843,7 +7835,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129963701</v>
+        <v>129963707</v>
       </c>
       <c r="B74" t="n">
         <v>79706</v>
@@ -7878,10 +7870,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435051</v>
+        <v>435035</v>
       </c>
       <c r="R74" t="n">
-        <v>6783226</v>
+        <v>6783349</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7940,45 +7932,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129963707</v>
+        <v>129963748</v>
       </c>
       <c r="B75" t="n">
-        <v>79706</v>
+        <v>56933</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435035</v>
+        <v>435072</v>
       </c>
       <c r="R75" t="n">
-        <v>6783349</v>
+        <v>6783347</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8730,10 +8730,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129963847</v>
+        <v>129963765</v>
       </c>
       <c r="B83" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8741,21 +8741,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435018</v>
+        <v>435080</v>
       </c>
       <c r="R83" t="n">
-        <v>6783344</v>
+        <v>6783254</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8827,7 +8827,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129963829</v>
+        <v>129963847</v>
       </c>
       <c r="B84" t="n">
         <v>79087</v>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435142</v>
+        <v>435018</v>
       </c>
       <c r="R84" t="n">
-        <v>6783234</v>
+        <v>6783344</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8898,11 +8898,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8929,10 +8924,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129963713</v>
+        <v>129963829</v>
       </c>
       <c r="B85" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8940,21 +8935,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8964,10 +8959,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434963</v>
+        <v>435142</v>
       </c>
       <c r="R85" t="n">
-        <v>6783297</v>
+        <v>6783234</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9000,6 +8995,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9026,44 +9026,35 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129963779</v>
+        <v>129963713</v>
       </c>
       <c r="B86" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
@@ -9073,7 +9064,7 @@
         <v>434963</v>
       </c>
       <c r="R86" t="n">
-        <v>6783366</v>
+        <v>6783297</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9114,7 +9105,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9133,45 +9123,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129963765</v>
+        <v>129963779</v>
       </c>
       <c r="B87" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435080</v>
+        <v>434963</v>
       </c>
       <c r="R87" t="n">
-        <v>6783254</v>
+        <v>6783366</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9212,6 +9211,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11408,45 +11408,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129963835</v>
+        <v>129963793</v>
       </c>
       <c r="B110" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>435082</v>
+        <v>434941</v>
       </c>
       <c r="R110" t="n">
-        <v>6783221</v>
+        <v>6783312</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11481,17 +11490,13 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11607,54 +11612,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129963793</v>
+        <v>129963835</v>
       </c>
       <c r="B112" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434941</v>
+        <v>435082</v>
       </c>
       <c r="R112" t="n">
-        <v>6783312</v>
+        <v>6783221</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11689,13 +11685,17 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11714,10 +11714,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129963852</v>
+        <v>129963693</v>
       </c>
       <c r="B113" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11725,21 +11725,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434938</v>
+        <v>435260</v>
       </c>
       <c r="R113" t="n">
-        <v>6783373</v>
+        <v>6783290</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11811,10 +11811,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129963844</v>
+        <v>129963698</v>
       </c>
       <c r="B114" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11822,21 +11822,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11846,10 +11846,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>435038</v>
+        <v>435103</v>
       </c>
       <c r="R114" t="n">
-        <v>6783417</v>
+        <v>6783246</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11882,11 +11882,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11913,45 +11908,54 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129963706</v>
+        <v>129963790</v>
       </c>
       <c r="B115" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>435067</v>
+        <v>435100</v>
       </c>
       <c r="R115" t="n">
-        <v>6783353</v>
+        <v>6783252</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11992,6 +11996,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12010,10 +12015,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129963740</v>
+        <v>129963852</v>
       </c>
       <c r="B116" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12021,42 +12026,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>435041</v>
+        <v>434938</v>
       </c>
       <c r="R116" t="n">
-        <v>6783374</v>
+        <v>6783373</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12115,10 +12112,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129963693</v>
+        <v>129963844</v>
       </c>
       <c r="B117" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12126,21 +12123,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12150,10 +12147,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>435260</v>
+        <v>435038</v>
       </c>
       <c r="R117" t="n">
-        <v>6783290</v>
+        <v>6783417</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12186,6 +12183,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12212,7 +12214,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129963698</v>
+        <v>129963706</v>
       </c>
       <c r="B118" t="n">
         <v>79706</v>
@@ -12247,10 +12249,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435103</v>
+        <v>435067</v>
       </c>
       <c r="R118" t="n">
-        <v>6783246</v>
+        <v>6783353</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12309,41 +12311,40 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129963790</v>
+        <v>129963740</v>
       </c>
       <c r="B119" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -12353,10 +12354,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435100</v>
+        <v>435041</v>
       </c>
       <c r="R119" t="n">
-        <v>6783252</v>
+        <v>6783374</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12397,7 +12398,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13016,10 +13016,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129963822</v>
+        <v>129963733</v>
       </c>
       <c r="B126" t="n">
-        <v>79087</v>
+        <v>57898</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13027,34 +13027,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>435060</v>
+        <v>435055</v>
       </c>
       <c r="R126" t="n">
-        <v>6783211</v>
+        <v>6783240</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13113,45 +13121,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129963841</v>
+        <v>129963783</v>
       </c>
       <c r="B127" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435105</v>
+        <v>435255</v>
       </c>
       <c r="R127" t="n">
-        <v>6783392</v>
+        <v>6783275</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13186,17 +13203,13 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13215,54 +13228,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129963783</v>
+        <v>129963822</v>
       </c>
       <c r="B128" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>435255</v>
+        <v>435060</v>
       </c>
       <c r="R128" t="n">
-        <v>6783275</v>
+        <v>6783211</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13303,7 +13307,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13322,10 +13325,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129963733</v>
+        <v>129963841</v>
       </c>
       <c r="B129" t="n">
-        <v>57898</v>
+        <v>79087</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13333,42 +13336,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435055</v>
+        <v>435105</v>
       </c>
       <c r="R129" t="n">
-        <v>6783240</v>
+        <v>6783392</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13401,6 +13396,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13427,10 +13427,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129963839</v>
+        <v>129963709</v>
       </c>
       <c r="B130" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13438,21 +13438,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>435149</v>
+        <v>435050</v>
       </c>
       <c r="R130" t="n">
-        <v>6783386</v>
+        <v>6783376</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13498,11 +13498,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13529,10 +13524,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129963709</v>
+        <v>129963839</v>
       </c>
       <c r="B131" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13540,21 +13535,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13564,10 +13559,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>435050</v>
+        <v>435149</v>
       </c>
       <c r="R131" t="n">
-        <v>6783376</v>
+        <v>6783386</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13600,6 +13595,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 7913-2025 artfynd.xlsx
+++ b/artfynd/A 7913-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129963682</v>
       </c>
       <c r="B2" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129963715</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129963697</v>
+        <v>129963800</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435140</v>
+        <v>435261</v>
       </c>
       <c r="R4" t="n">
-        <v>6783274</v>
+        <v>6783290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129963800</v>
+        <v>129963697</v>
       </c>
       <c r="B5" t="n">
-        <v>78844</v>
+        <v>79707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435261</v>
+        <v>435140</v>
       </c>
       <c r="R5" t="n">
-        <v>6783290</v>
+        <v>6783274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129963742</v>
+        <v>129963799</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,42 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434938</v>
+        <v>435115</v>
       </c>
       <c r="R6" t="n">
-        <v>6783317</v>
+        <v>6783224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129963785</v>
+        <v>129963684</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435286</v>
+        <v>435069</v>
       </c>
       <c r="R7" t="n">
-        <v>6783280</v>
+        <v>6783183</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,7 +1239,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1275,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129963768</v>
+        <v>129963806</v>
       </c>
       <c r="B8" t="n">
         <v>78845</v>
@@ -1286,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435080</v>
+        <v>434862</v>
       </c>
       <c r="R8" t="n">
-        <v>6783283</v>
+        <v>6783373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129963799</v>
+        <v>129963742</v>
       </c>
       <c r="B9" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,34 +1365,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435115</v>
+        <v>434938</v>
       </c>
       <c r="R9" t="n">
-        <v>6783224</v>
+        <v>6783317</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,45 +1459,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129963684</v>
+        <v>129963785</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435069</v>
+        <v>435286</v>
       </c>
       <c r="R10" t="n">
-        <v>6783183</v>
+        <v>6783280</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,6 +1547,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129963806</v>
+        <v>129963768</v>
       </c>
       <c r="B11" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434862</v>
+        <v>435080</v>
       </c>
       <c r="R11" t="n">
-        <v>6783373</v>
+        <v>6783283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
         <v>129963843</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>129963838</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129963775</v>
       </c>
       <c r="B14" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129963760</v>
       </c>
       <c r="B15" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129963774</v>
       </c>
       <c r="B16" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129963778</v>
       </c>
       <c r="B17" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129963830</v>
+        <v>129963694</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435195</v>
+        <v>435287</v>
       </c>
       <c r="R18" t="n">
-        <v>6783259</v>
+        <v>6783290</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129963850</v>
+        <v>129963798</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2367,21 +2367,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434979</v>
+        <v>435226</v>
       </c>
       <c r="R19" t="n">
-        <v>6783324</v>
+        <v>6783162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2453,10 +2453,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129963849</v>
+        <v>129963830</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434989</v>
+        <v>435195</v>
       </c>
       <c r="R20" t="n">
-        <v>6783322</v>
+        <v>6783259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129963694</v>
+        <v>129963850</v>
       </c>
       <c r="B21" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435287</v>
+        <v>434979</v>
       </c>
       <c r="R21" t="n">
-        <v>6783290</v>
+        <v>6783324</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129963798</v>
+        <v>129963849</v>
       </c>
       <c r="B22" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435226</v>
+        <v>434989</v>
       </c>
       <c r="R22" t="n">
-        <v>6783162</v>
+        <v>6783322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2747,7 +2747,7 @@
         <v>129963758</v>
       </c>
       <c r="B23" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129963827</v>
+        <v>129963739</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,34 +3066,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435224</v>
+        <v>435244</v>
       </c>
       <c r="R26" t="n">
-        <v>6783121</v>
+        <v>6783276</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129963848</v>
+        <v>129963827</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3187,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434993</v>
+        <v>435224</v>
       </c>
       <c r="R27" t="n">
-        <v>6783317</v>
+        <v>6783121</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3223,11 +3231,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3254,10 +3257,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129963831</v>
+        <v>129963848</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3289,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435239</v>
+        <v>434993</v>
       </c>
       <c r="R28" t="n">
-        <v>6783254</v>
+        <v>6783317</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3325,6 +3328,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3351,10 +3359,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129963714</v>
+        <v>129963831</v>
       </c>
       <c r="B29" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3362,21 +3370,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3386,10 +3394,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434952</v>
+        <v>435239</v>
       </c>
       <c r="R29" t="n">
-        <v>6783307</v>
+        <v>6783254</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,10 +3456,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963770</v>
+        <v>129963714</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3459,21 +3467,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3483,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435151</v>
+        <v>434952</v>
       </c>
       <c r="R30" t="n">
-        <v>6783386</v>
+        <v>6783307</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3545,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129963723</v>
+        <v>129963770</v>
       </c>
       <c r="B31" t="n">
-        <v>79677</v>
+        <v>78846</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3556,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3580,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435137</v>
+        <v>435151</v>
       </c>
       <c r="R31" t="n">
-        <v>6783270</v>
+        <v>6783386</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3642,10 +3650,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129963739</v>
+        <v>129963723</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,42 +3661,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435244</v>
+        <v>435137</v>
       </c>
       <c r="R32" t="n">
-        <v>6783276</v>
+        <v>6783270</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
         <v>129963803</v>
       </c>
       <c r="B33" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129963762</v>
+        <v>129963842</v>
       </c>
       <c r="B34" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435102</v>
+        <v>435074</v>
       </c>
       <c r="R34" t="n">
-        <v>6783245</v>
+        <v>6783347</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3941,10 +3946,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129963719</v>
+        <v>129963834</v>
       </c>
       <c r="B35" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3952,21 +3957,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435236</v>
+        <v>435136</v>
       </c>
       <c r="R35" t="n">
-        <v>6783256</v>
+        <v>6783253</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,6 +4017,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4038,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129963724</v>
+        <v>129963762</v>
       </c>
       <c r="B36" t="n">
-        <v>79677</v>
+        <v>78846</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4049,21 +4059,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4073,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435055</v>
+        <v>435102</v>
       </c>
       <c r="R36" t="n">
-        <v>6783236</v>
+        <v>6783245</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4135,10 +4145,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129963767</v>
+        <v>129963719</v>
       </c>
       <c r="B37" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4146,21 +4156,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4170,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435066</v>
+        <v>435236</v>
       </c>
       <c r="R37" t="n">
-        <v>6783276</v>
+        <v>6783256</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4232,10 +4242,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129963842</v>
+        <v>129963724</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4243,21 +4253,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4267,10 +4277,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435074</v>
+        <v>435055</v>
       </c>
       <c r="R38" t="n">
-        <v>6783347</v>
+        <v>6783236</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4303,11 +4313,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4334,10 +4339,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129963834</v>
+        <v>129963767</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4345,21 +4350,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4374,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435136</v>
+        <v>435066</v>
       </c>
       <c r="R39" t="n">
-        <v>6783253</v>
+        <v>6783276</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4405,11 +4410,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129963731</v>
+        <v>129963750</v>
       </c>
       <c r="B40" t="n">
-        <v>91569</v>
+        <v>78846</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434932</v>
+        <v>435002</v>
       </c>
       <c r="R40" t="n">
-        <v>6783346</v>
+        <v>6783275</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4515,29 +4515,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4554,10 +4533,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129963854</v>
+        <v>129963705</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4565,21 +4544,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4589,10 +4568,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434905</v>
+        <v>435151</v>
       </c>
       <c r="R41" t="n">
-        <v>6783388</v>
+        <v>6783380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4651,32 +4630,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129963705</v>
+        <v>129963731</v>
       </c>
       <c r="B42" t="n">
-        <v>79706</v>
+        <v>91570</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4665,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435151</v>
+        <v>434932</v>
       </c>
       <c r="R42" t="n">
-        <v>6783380</v>
+        <v>6783346</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4730,8 +4709,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4748,10 +4748,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129963738</v>
+        <v>129963854</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4759,42 +4759,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435231</v>
+        <v>434905</v>
       </c>
       <c r="R43" t="n">
-        <v>6783171</v>
+        <v>6783388</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,7 +4845,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129963743</v>
+        <v>129963738</v>
       </c>
       <c r="B44" t="n">
         <v>57737</v>
@@ -4886,7 +4878,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4896,10 +4888,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434936</v>
+        <v>435231</v>
       </c>
       <c r="R44" t="n">
-        <v>6783319</v>
+        <v>6783171</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4958,7 +4950,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129963737</v>
+        <v>129963743</v>
       </c>
       <c r="B45" t="n">
         <v>57737</v>
@@ -5001,10 +4993,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435238</v>
+        <v>434936</v>
       </c>
       <c r="R45" t="n">
-        <v>6783110</v>
+        <v>6783319</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5063,10 +5055,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129963750</v>
+        <v>129963737</v>
       </c>
       <c r="B46" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5074,34 +5066,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435002</v>
+        <v>435238</v>
       </c>
       <c r="R46" t="n">
-        <v>6783275</v>
+        <v>6783110</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129963804</v>
+        <v>129963759</v>
       </c>
       <c r="B48" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5278,21 +5278,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435116</v>
+        <v>435138</v>
       </c>
       <c r="R48" t="n">
-        <v>6783395</v>
+        <v>6783290</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5364,10 +5364,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129963801</v>
+        <v>129963718</v>
       </c>
       <c r="B49" t="n">
-        <v>78844</v>
+        <v>79678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5375,21 +5375,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435140</v>
+        <v>435195</v>
       </c>
       <c r="R49" t="n">
-        <v>6783274</v>
+        <v>6783256</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5568,10 +5568,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129963718</v>
+        <v>129963804</v>
       </c>
       <c r="B51" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5579,21 +5579,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435195</v>
+        <v>435116</v>
       </c>
       <c r="R51" t="n">
-        <v>6783256</v>
+        <v>6783395</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5665,10 +5665,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129963823</v>
+        <v>129963703</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5700,10 +5700,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435065</v>
+        <v>435072</v>
       </c>
       <c r="R52" t="n">
-        <v>6783208</v>
+        <v>6783251</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129963703</v>
+        <v>129963801</v>
       </c>
       <c r="B53" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435072</v>
+        <v>435140</v>
       </c>
       <c r="R53" t="n">
-        <v>6783251</v>
+        <v>6783274</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5859,10 +5859,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129963759</v>
+        <v>129963823</v>
       </c>
       <c r="B54" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5870,21 +5870,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435138</v>
+        <v>435065</v>
       </c>
       <c r="R54" t="n">
-        <v>6783290</v>
+        <v>6783208</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5956,10 +5956,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129963763</v>
+        <v>129963696</v>
       </c>
       <c r="B55" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435052</v>
+        <v>435135</v>
       </c>
       <c r="R55" t="n">
-        <v>6783227</v>
+        <v>6783269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6053,10 +6053,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129963696</v>
+        <v>129963708</v>
       </c>
       <c r="B56" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435135</v>
+        <v>435013</v>
       </c>
       <c r="R56" t="n">
-        <v>6783269</v>
+        <v>6783367</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129963708</v>
+        <v>129963681</v>
       </c>
       <c r="B57" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435013</v>
+        <v>435046</v>
       </c>
       <c r="R57" t="n">
-        <v>6783367</v>
+        <v>6783227</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129963681</v>
+        <v>129963846</v>
       </c>
       <c r="B58" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6258,21 +6258,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435046</v>
+        <v>435021</v>
       </c>
       <c r="R58" t="n">
-        <v>6783227</v>
+        <v>6783388</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6344,45 +6344,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129963846</v>
+        <v>129963782</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435021</v>
+        <v>435240</v>
       </c>
       <c r="R59" t="n">
-        <v>6783388</v>
+        <v>6783151</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6423,6 +6432,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6441,10 +6451,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129963746</v>
+        <v>129963749</v>
       </c>
       <c r="B60" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6452,42 +6462,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434861</v>
+        <v>434946</v>
       </c>
       <c r="R60" t="n">
-        <v>6783366</v>
+        <v>6783406</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6546,54 +6548,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129963856</v>
+        <v>129963763</v>
       </c>
       <c r="B61" t="n">
-        <v>5177</v>
+        <v>78846</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435075</v>
+        <v>435052</v>
       </c>
       <c r="R61" t="n">
-        <v>6783111</v>
+        <v>6783227</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6634,7 +6627,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6653,54 +6645,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129963782</v>
+        <v>129963720</v>
       </c>
       <c r="B62" t="n">
-        <v>8451</v>
+        <v>79678</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435240</v>
+        <v>435263</v>
       </c>
       <c r="R62" t="n">
-        <v>6783151</v>
+        <v>6783286</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6741,7 +6724,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6760,10 +6742,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129963749</v>
+        <v>129963753</v>
       </c>
       <c r="B63" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6795,10 +6777,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434946</v>
+        <v>435074</v>
       </c>
       <c r="R63" t="n">
-        <v>6783406</v>
+        <v>6783208</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6857,10 +6839,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129963720</v>
+        <v>129963727</v>
       </c>
       <c r="B64" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6892,10 +6874,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435263</v>
+        <v>435156</v>
       </c>
       <c r="R64" t="n">
-        <v>6783286</v>
+        <v>6783404</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6954,10 +6936,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129963753</v>
+        <v>129963746</v>
       </c>
       <c r="B65" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6965,34 +6947,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>435074</v>
+        <v>434861</v>
       </c>
       <c r="R65" t="n">
-        <v>6783208</v>
+        <v>6783366</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7051,45 +7041,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129963727</v>
+        <v>129963856</v>
       </c>
       <c r="B66" t="n">
-        <v>79677</v>
+        <v>5177</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435156</v>
+        <v>435075</v>
       </c>
       <c r="R66" t="n">
-        <v>6783404</v>
+        <v>6783111</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7130,6 +7129,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7148,10 +7148,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129963735</v>
+        <v>129963701</v>
       </c>
       <c r="B67" t="n">
-        <v>57898</v>
+        <v>79707</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7159,42 +7159,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435028</v>
+        <v>435051</v>
       </c>
       <c r="R67" t="n">
-        <v>6783350</v>
+        <v>6783226</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7253,10 +7245,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129963761</v>
+        <v>129963707</v>
       </c>
       <c r="B68" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7264,21 +7256,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7288,10 +7280,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435140</v>
+        <v>435035</v>
       </c>
       <c r="R68" t="n">
-        <v>6783272</v>
+        <v>6783349</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7350,10 +7342,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129963764</v>
+        <v>129963688</v>
       </c>
       <c r="B69" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7361,21 +7353,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7385,10 +7377,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435059</v>
+        <v>435226</v>
       </c>
       <c r="R69" t="n">
-        <v>6783248</v>
+        <v>6783162</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7447,10 +7439,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129963728</v>
+        <v>129963837</v>
       </c>
       <c r="B70" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7458,21 +7450,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7482,10 +7474,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435152</v>
+        <v>435094</v>
       </c>
       <c r="R70" t="n">
-        <v>6783393</v>
+        <v>6783352</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7544,10 +7536,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129963701</v>
+        <v>129963764</v>
       </c>
       <c r="B71" t="n">
-        <v>79706</v>
+        <v>78846</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7555,21 +7547,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7579,10 +7571,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435051</v>
+        <v>435059</v>
       </c>
       <c r="R71" t="n">
-        <v>6783226</v>
+        <v>6783248</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7641,45 +7633,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129963688</v>
+        <v>129963748</v>
       </c>
       <c r="B72" t="n">
-        <v>79706</v>
+        <v>56933</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435226</v>
+        <v>435072</v>
       </c>
       <c r="R72" t="n">
-        <v>6783162</v>
+        <v>6783347</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7738,10 +7738,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129963837</v>
+        <v>129963735</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>57898</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7749,34 +7749,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435094</v>
+        <v>435028</v>
       </c>
       <c r="R73" t="n">
-        <v>6783352</v>
+        <v>6783350</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7835,10 +7843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129963707</v>
+        <v>129963761</v>
       </c>
       <c r="B74" t="n">
-        <v>79706</v>
+        <v>78846</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7846,21 +7854,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7870,10 +7878,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435035</v>
+        <v>435140</v>
       </c>
       <c r="R74" t="n">
-        <v>6783349</v>
+        <v>6783272</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7932,53 +7940,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129963748</v>
+        <v>129963728</v>
       </c>
       <c r="B75" t="n">
-        <v>56933</v>
+        <v>79678</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435072</v>
+        <v>435152</v>
       </c>
       <c r="R75" t="n">
-        <v>6783347</v>
+        <v>6783393</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129963853</v>
+        <v>129963689</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8048,37 +8048,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434958</v>
+        <v>435225</v>
       </c>
       <c r="R76" t="n">
-        <v>6783365</v>
+        <v>6783144</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8119,7 +8116,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8138,10 +8134,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129963820</v>
+        <v>129963704</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8149,21 +8145,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8173,10 +8169,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435070</v>
+        <v>435073</v>
       </c>
       <c r="R77" t="n">
-        <v>6783207</v>
+        <v>6783319</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8235,10 +8231,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129963689</v>
+        <v>129963853</v>
       </c>
       <c r="B78" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8246,34 +8242,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435225</v>
+        <v>434958</v>
       </c>
       <c r="R78" t="n">
-        <v>6783144</v>
+        <v>6783365</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8314,6 +8313,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8332,10 +8332,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129963704</v>
+        <v>129963820</v>
       </c>
       <c r="B79" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8343,21 +8343,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435073</v>
+        <v>435070</v>
       </c>
       <c r="R79" t="n">
-        <v>6783319</v>
+        <v>6783207</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8539,7 +8539,7 @@
         <v>129963717</v>
       </c>
       <c r="B81" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>129963716</v>
       </c>
       <c r="B82" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8730,10 +8730,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129963765</v>
+        <v>129963713</v>
       </c>
       <c r="B83" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8741,21 +8741,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435080</v>
+        <v>434963</v>
       </c>
       <c r="R83" t="n">
-        <v>6783254</v>
+        <v>6783297</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8830,7 +8830,7 @@
         <v>129963847</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>129963829</v>
       </c>
       <c r="B85" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9026,35 +9026,44 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129963713</v>
+        <v>129963779</v>
       </c>
       <c r="B86" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
@@ -9064,7 +9073,7 @@
         <v>434963</v>
       </c>
       <c r="R86" t="n">
-        <v>6783297</v>
+        <v>6783366</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9105,6 +9114,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9123,54 +9133,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129963779</v>
+        <v>129963765</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434963</v>
+        <v>435080</v>
       </c>
       <c r="R87" t="n">
-        <v>6783366</v>
+        <v>6783254</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9211,7 +9212,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9230,10 +9230,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129963825</v>
+        <v>129963710</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9241,21 +9241,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>435247</v>
+        <v>435047</v>
       </c>
       <c r="R88" t="n">
-        <v>6783126</v>
+        <v>6783384</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129963832</v>
+        <v>129963691</v>
       </c>
       <c r="B89" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9338,21 +9338,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9362,10 +9362,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>435150</v>
+        <v>435115</v>
       </c>
       <c r="R89" t="n">
-        <v>6783272</v>
+        <v>6783224</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9424,10 +9424,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129963710</v>
+        <v>129963692</v>
       </c>
       <c r="B90" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>435047</v>
+        <v>435238</v>
       </c>
       <c r="R90" t="n">
-        <v>6783384</v>
+        <v>6783256</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9521,10 +9521,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129963691</v>
+        <v>129963825</v>
       </c>
       <c r="B91" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>435115</v>
+        <v>435247</v>
       </c>
       <c r="R91" t="n">
-        <v>6783224</v>
+        <v>6783126</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129963692</v>
+        <v>129963832</v>
       </c>
       <c r="B92" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9653,10 +9653,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435238</v>
+        <v>435150</v>
       </c>
       <c r="R92" t="n">
-        <v>6783256</v>
+        <v>6783272</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9822,10 +9822,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129963686</v>
+        <v>129963826</v>
       </c>
       <c r="B94" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9833,21 +9833,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>435088</v>
+        <v>435250</v>
       </c>
       <c r="R94" t="n">
-        <v>6783097</v>
+        <v>6783158</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9919,10 +9919,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129963680</v>
+        <v>129963686</v>
       </c>
       <c r="B95" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>434999</v>
+        <v>435088</v>
       </c>
       <c r="R95" t="n">
-        <v>6783278</v>
+        <v>6783097</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10019,7 +10019,7 @@
         <v>129963711</v>
       </c>
       <c r="B96" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129963802</v>
+        <v>129963680</v>
       </c>
       <c r="B97" t="n">
-        <v>78844</v>
+        <v>79707</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10124,21 +10124,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10148,10 +10148,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>435056</v>
+        <v>434999</v>
       </c>
       <c r="R97" t="n">
-        <v>6783229</v>
+        <v>6783278</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10210,7 +10210,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129963757</v>
+        <v>129963802</v>
       </c>
       <c r="B98" t="n">
         <v>78845</v>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>435226</v>
+        <v>435056</v>
       </c>
       <c r="R98" t="n">
-        <v>6783162</v>
+        <v>6783229</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10307,10 +10307,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129963777</v>
+        <v>129963745</v>
       </c>
       <c r="B99" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10318,34 +10318,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434863</v>
+        <v>434942</v>
       </c>
       <c r="R99" t="n">
-        <v>6783373</v>
+        <v>6783348</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10404,10 +10412,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129963826</v>
+        <v>129963744</v>
       </c>
       <c r="B100" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10415,34 +10423,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>435250</v>
+        <v>434931</v>
       </c>
       <c r="R100" t="n">
-        <v>6783158</v>
+        <v>6783336</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10501,10 +10517,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129963745</v>
+        <v>129963757</v>
       </c>
       <c r="B101" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10512,42 +10528,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434942</v>
+        <v>435226</v>
       </c>
       <c r="R101" t="n">
-        <v>6783348</v>
+        <v>6783162</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10606,10 +10614,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129963744</v>
+        <v>129963777</v>
       </c>
       <c r="B102" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10617,42 +10625,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434931</v>
+        <v>434863</v>
       </c>
       <c r="R102" t="n">
-        <v>6783336</v>
+        <v>6783373</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10711,10 +10711,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129963821</v>
+        <v>129963687</v>
       </c>
       <c r="B103" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10722,21 +10722,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>435042</v>
+        <v>435243</v>
       </c>
       <c r="R103" t="n">
-        <v>6783226</v>
+        <v>6783165</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129963687</v>
+        <v>129963712</v>
       </c>
       <c r="B104" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>435243</v>
+        <v>434998</v>
       </c>
       <c r="R104" t="n">
-        <v>6783165</v>
+        <v>6783407</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10905,10 +10905,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129963712</v>
+        <v>129963747</v>
       </c>
       <c r="B105" t="n">
-        <v>79706</v>
+        <v>56313</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10916,34 +10916,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>206004</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>434998</v>
+        <v>435173</v>
       </c>
       <c r="R105" t="n">
-        <v>6783407</v>
+        <v>6783096</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11002,54 +11010,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129963791</v>
+        <v>129963821</v>
       </c>
       <c r="B106" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>435076</v>
+        <v>435042</v>
       </c>
       <c r="R106" t="n">
-        <v>6783364</v>
+        <v>6783226</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11090,7 +11089,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11109,45 +11107,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129963752</v>
+        <v>129963791</v>
       </c>
       <c r="B107" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>435046</v>
+        <v>435076</v>
       </c>
       <c r="R107" t="n">
-        <v>6783227</v>
+        <v>6783364</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11188,6 +11195,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11206,10 +11214,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129963754</v>
+        <v>129963752</v>
       </c>
       <c r="B108" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11241,10 +11249,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>435094</v>
+        <v>435046</v>
       </c>
       <c r="R108" t="n">
-        <v>6783192</v>
+        <v>6783227</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11303,10 +11311,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129963747</v>
+        <v>129963754</v>
       </c>
       <c r="B109" t="n">
-        <v>56313</v>
+        <v>78846</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11314,42 +11322,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>206004</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>435173</v>
+        <v>435094</v>
       </c>
       <c r="R109" t="n">
-        <v>6783096</v>
+        <v>6783192</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11408,54 +11408,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129963793</v>
+        <v>129963835</v>
       </c>
       <c r="B110" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434941</v>
+        <v>435082</v>
       </c>
       <c r="R110" t="n">
-        <v>6783312</v>
+        <v>6783221</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11490,13 +11481,17 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11515,45 +11510,54 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129963772</v>
+        <v>129963793</v>
       </c>
       <c r="B111" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>435050</v>
+        <v>434941</v>
       </c>
       <c r="R111" t="n">
-        <v>6783382</v>
+        <v>6783312</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11594,6 +11598,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11612,10 +11617,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129963835</v>
+        <v>129963772</v>
       </c>
       <c r="B112" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11623,21 +11628,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11647,10 +11652,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>435082</v>
+        <v>435050</v>
       </c>
       <c r="R112" t="n">
-        <v>6783221</v>
+        <v>6783382</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11683,11 +11688,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11714,10 +11714,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129963693</v>
+        <v>129963852</v>
       </c>
       <c r="B113" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11725,21 +11725,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>435260</v>
+        <v>434938</v>
       </c>
       <c r="R113" t="n">
-        <v>6783290</v>
+        <v>6783373</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11811,10 +11811,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129963698</v>
+        <v>129963844</v>
       </c>
       <c r="B114" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11822,21 +11822,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11846,10 +11846,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>435103</v>
+        <v>435038</v>
       </c>
       <c r="R114" t="n">
-        <v>6783246</v>
+        <v>6783417</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11882,6 +11882,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12015,10 +12020,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129963852</v>
+        <v>129963706</v>
       </c>
       <c r="B116" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12026,21 +12031,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12050,10 +12055,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434938</v>
+        <v>435067</v>
       </c>
       <c r="R116" t="n">
-        <v>6783373</v>
+        <v>6783353</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12112,10 +12117,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129963844</v>
+        <v>129963693</v>
       </c>
       <c r="B117" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12123,21 +12128,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12147,10 +12152,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>435038</v>
+        <v>435260</v>
       </c>
       <c r="R117" t="n">
-        <v>6783417</v>
+        <v>6783290</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12183,11 +12188,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12214,10 +12214,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129963706</v>
+        <v>129963698</v>
       </c>
       <c r="B118" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12249,10 +12249,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435067</v>
+        <v>435103</v>
       </c>
       <c r="R118" t="n">
-        <v>6783353</v>
+        <v>6783246</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129963741</v>
+        <v>129963805</v>
       </c>
       <c r="B120" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12427,42 +12427,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435038</v>
+        <v>435113</v>
       </c>
       <c r="R120" t="n">
-        <v>6783388</v>
+        <v>6783386</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12521,10 +12513,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129963845</v>
+        <v>129963741</v>
       </c>
       <c r="B121" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12532,34 +12524,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435002</v>
+        <v>435038</v>
       </c>
       <c r="R121" t="n">
-        <v>6783412</v>
+        <v>6783388</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12618,45 +12618,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129963805</v>
+        <v>129963780</v>
       </c>
       <c r="B122" t="n">
-        <v>78844</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>435113</v>
+        <v>435085</v>
       </c>
       <c r="R122" t="n">
-        <v>6783386</v>
+        <v>6783160</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12697,6 +12706,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12715,54 +12725,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129963780</v>
+        <v>129963751</v>
       </c>
       <c r="B123" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>435085</v>
+        <v>434998</v>
       </c>
       <c r="R123" t="n">
-        <v>6783160</v>
+        <v>6783271</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12803,7 +12804,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12822,10 +12822,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129963751</v>
+        <v>129963722</v>
       </c>
       <c r="B124" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12833,21 +12833,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>434998</v>
+        <v>435197</v>
       </c>
       <c r="R124" t="n">
-        <v>6783271</v>
+        <v>6783294</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129963722</v>
+        <v>129963845</v>
       </c>
       <c r="B125" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12930,21 +12930,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12954,10 +12954,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435197</v>
+        <v>435002</v>
       </c>
       <c r="R125" t="n">
-        <v>6783294</v>
+        <v>6783412</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13016,10 +13016,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129963733</v>
+        <v>129963822</v>
       </c>
       <c r="B126" t="n">
-        <v>57898</v>
+        <v>79088</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13027,42 +13027,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>435055</v>
+        <v>435060</v>
       </c>
       <c r="R126" t="n">
-        <v>6783240</v>
+        <v>6783211</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13121,54 +13113,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129963783</v>
+        <v>129963841</v>
       </c>
       <c r="B127" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435255</v>
+        <v>435105</v>
       </c>
       <c r="R127" t="n">
-        <v>6783275</v>
+        <v>6783392</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13203,13 +13186,17 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13228,10 +13215,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129963822</v>
+        <v>129963733</v>
       </c>
       <c r="B128" t="n">
-        <v>79087</v>
+        <v>57898</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13239,34 +13226,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>435060</v>
+        <v>435055</v>
       </c>
       <c r="R128" t="n">
-        <v>6783211</v>
+        <v>6783240</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13325,45 +13320,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129963841</v>
+        <v>129963783</v>
       </c>
       <c r="B129" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435105</v>
+        <v>435255</v>
       </c>
       <c r="R129" t="n">
-        <v>6783392</v>
+        <v>6783275</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13398,17 +13402,13 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13430,7 +13430,7 @@
         <v>129963709</v>
       </c>
       <c r="B130" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>129963839</v>
       </c>
       <c r="B131" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129963851</v>
+        <v>129963828</v>
       </c>
       <c r="B133" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13768,10 +13768,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>434938</v>
+        <v>435102</v>
       </c>
       <c r="R133" t="n">
-        <v>6783327</v>
+        <v>6783177</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13804,6 +13804,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13830,10 +13835,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129963836</v>
+        <v>129963851</v>
       </c>
       <c r="B134" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13865,10 +13870,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>435073</v>
+        <v>434938</v>
       </c>
       <c r="R134" t="n">
-        <v>6783270</v>
+        <v>6783327</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13901,11 +13906,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13932,10 +13932,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129963683</v>
+        <v>129963836</v>
       </c>
       <c r="B135" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13943,21 +13943,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13967,10 +13967,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>435093</v>
+        <v>435073</v>
       </c>
       <c r="R135" t="n">
-        <v>6783192</v>
+        <v>6783270</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14003,6 +14003,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14029,10 +14034,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129963699</v>
+        <v>129963756</v>
       </c>
       <c r="B136" t="n">
-        <v>79706</v>
+        <v>78846</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14040,21 +14045,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14064,10 +14069,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>435081</v>
+        <v>435087</v>
       </c>
       <c r="R136" t="n">
-        <v>6783223</v>
+        <v>6783099</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14126,10 +14131,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129963702</v>
+        <v>129963725</v>
       </c>
       <c r="B137" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14137,21 +14142,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14161,10 +14166,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>435064</v>
+        <v>435062</v>
       </c>
       <c r="R137" t="n">
-        <v>6783239</v>
+        <v>6783268</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14223,10 +14228,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129963828</v>
+        <v>129963769</v>
       </c>
       <c r="B138" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14234,21 +14239,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14258,10 +14263,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>435102</v>
+        <v>435072</v>
       </c>
       <c r="R138" t="n">
-        <v>6783177</v>
+        <v>6783317</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14294,11 +14299,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14325,10 +14325,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129963725</v>
+        <v>129963699</v>
       </c>
       <c r="B139" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14336,21 +14336,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14360,10 +14360,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>435062</v>
+        <v>435081</v>
       </c>
       <c r="R139" t="n">
-        <v>6783268</v>
+        <v>6783223</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14422,10 +14422,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129963700</v>
+        <v>129963683</v>
       </c>
       <c r="B140" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14457,10 +14457,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>435068</v>
+        <v>435093</v>
       </c>
       <c r="R140" t="n">
-        <v>6783233</v>
+        <v>6783192</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14519,10 +14519,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129963690</v>
+        <v>129963700</v>
       </c>
       <c r="B141" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14554,10 +14554,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>435121</v>
+        <v>435068</v>
       </c>
       <c r="R141" t="n">
-        <v>6783166</v>
+        <v>6783233</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14616,10 +14616,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129963756</v>
+        <v>129963690</v>
       </c>
       <c r="B142" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14627,21 +14627,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14651,10 +14651,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>435087</v>
+        <v>435121</v>
       </c>
       <c r="R142" t="n">
-        <v>6783099</v>
+        <v>6783166</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14713,10 +14713,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129963769</v>
+        <v>129963702</v>
       </c>
       <c r="B143" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14724,21 +14724,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14748,10 +14748,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>435072</v>
+        <v>435064</v>
       </c>
       <c r="R143" t="n">
-        <v>6783317</v>
+        <v>6783239</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 7913-2025 artfynd.xlsx
+++ b/artfynd/A 7913-2025 artfynd.xlsx
@@ -2259,45 +2259,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129963694</v>
+        <v>129963792</v>
       </c>
       <c r="B18" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435287</v>
+        <v>435029</v>
       </c>
       <c r="R18" t="n">
-        <v>6783290</v>
+        <v>6783411</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,6 +2347,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2356,45 +2366,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129963798</v>
+        <v>129963784</v>
       </c>
       <c r="B19" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435226</v>
+        <v>435269</v>
       </c>
       <c r="R19" t="n">
-        <v>6783162</v>
+        <v>6783269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,6 +2454,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2453,10 +2473,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129963830</v>
+        <v>129963758</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2464,21 +2484,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,10 +2508,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435195</v>
+        <v>435121</v>
       </c>
       <c r="R20" t="n">
-        <v>6783259</v>
+        <v>6783166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,10 +2570,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129963850</v>
+        <v>129963694</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,21 +2581,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434979</v>
+        <v>435287</v>
       </c>
       <c r="R21" t="n">
-        <v>6783324</v>
+        <v>6783290</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,10 +2667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129963849</v>
+        <v>129963798</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2658,21 +2678,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2682,10 +2702,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434989</v>
+        <v>435226</v>
       </c>
       <c r="R22" t="n">
-        <v>6783322</v>
+        <v>6783162</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2744,10 +2764,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129963758</v>
+        <v>129963830</v>
       </c>
       <c r="B23" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2755,21 +2775,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2779,10 +2799,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435121</v>
+        <v>435195</v>
       </c>
       <c r="R23" t="n">
-        <v>6783166</v>
+        <v>6783259</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2841,54 +2861,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129963792</v>
+        <v>129963850</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435029</v>
+        <v>434979</v>
       </c>
       <c r="R24" t="n">
-        <v>6783411</v>
+        <v>6783324</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2929,7 +2940,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2948,54 +2958,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129963784</v>
+        <v>129963849</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435269</v>
+        <v>434989</v>
       </c>
       <c r="R25" t="n">
-        <v>6783269</v>
+        <v>6783322</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3036,7 +3037,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129963739</v>
+        <v>129963714</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,42 +3066,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435244</v>
+        <v>434952</v>
       </c>
       <c r="R26" t="n">
-        <v>6783276</v>
+        <v>6783307</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,10 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129963714</v>
+        <v>129963723</v>
       </c>
       <c r="B30" t="n">
-        <v>79707</v>
+        <v>79678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3467,21 +3459,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3483,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434952</v>
+        <v>435137</v>
       </c>
       <c r="R30" t="n">
-        <v>6783307</v>
+        <v>6783270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,10 +3545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129963770</v>
+        <v>129963739</v>
       </c>
       <c r="B31" t="n">
-        <v>78846</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,34 +3556,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435151</v>
+        <v>435244</v>
       </c>
       <c r="R31" t="n">
-        <v>6783386</v>
+        <v>6783276</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,10 +3650,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129963723</v>
+        <v>129963770</v>
       </c>
       <c r="B32" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3661,21 +3661,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435137</v>
+        <v>435151</v>
       </c>
       <c r="R32" t="n">
-        <v>6783270</v>
+        <v>6783386</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -6344,41 +6344,40 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129963782</v>
+        <v>129963746</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6388,10 +6387,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435240</v>
+        <v>434861</v>
       </c>
       <c r="R59" t="n">
-        <v>6783151</v>
+        <v>6783366</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6432,7 +6431,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6451,45 +6449,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129963749</v>
+        <v>129963856</v>
       </c>
       <c r="B60" t="n">
-        <v>78846</v>
+        <v>5177</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434946</v>
+        <v>435075</v>
       </c>
       <c r="R60" t="n">
-        <v>6783406</v>
+        <v>6783111</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6530,6 +6537,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6548,7 +6556,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129963763</v>
+        <v>129963749</v>
       </c>
       <c r="B61" t="n">
         <v>78846</v>
@@ -6583,10 +6591,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435052</v>
+        <v>434946</v>
       </c>
       <c r="R61" t="n">
-        <v>6783227</v>
+        <v>6783406</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6645,10 +6653,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129963720</v>
+        <v>129963763</v>
       </c>
       <c r="B62" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6656,21 +6664,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6680,10 +6688,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435263</v>
+        <v>435052</v>
       </c>
       <c r="R62" t="n">
-        <v>6783286</v>
+        <v>6783227</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6742,10 +6750,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129963753</v>
+        <v>129963720</v>
       </c>
       <c r="B63" t="n">
-        <v>78846</v>
+        <v>79678</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6753,21 +6761,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6777,10 +6785,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435074</v>
+        <v>435263</v>
       </c>
       <c r="R63" t="n">
-        <v>6783208</v>
+        <v>6783286</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6839,10 +6847,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129963727</v>
+        <v>129963753</v>
       </c>
       <c r="B64" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6850,21 +6858,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6874,10 +6882,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435156</v>
+        <v>435074</v>
       </c>
       <c r="R64" t="n">
-        <v>6783404</v>
+        <v>6783208</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6936,10 +6944,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129963746</v>
+        <v>129963727</v>
       </c>
       <c r="B65" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6947,42 +6955,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434861</v>
+        <v>435156</v>
       </c>
       <c r="R65" t="n">
-        <v>6783366</v>
+        <v>6783404</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7041,10 +7041,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129963856</v>
+        <v>129963782</v>
       </c>
       <c r="B66" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7052,21 +7052,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435075</v>
+        <v>435240</v>
       </c>
       <c r="R66" t="n">
-        <v>6783111</v>
+        <v>6783151</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9230,10 +9230,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129963710</v>
+        <v>129963825</v>
       </c>
       <c r="B88" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9241,21 +9241,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>435047</v>
+        <v>435247</v>
       </c>
       <c r="R88" t="n">
-        <v>6783384</v>
+        <v>6783126</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129963691</v>
+        <v>129963832</v>
       </c>
       <c r="B89" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9338,21 +9338,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9362,10 +9362,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>435115</v>
+        <v>435150</v>
       </c>
       <c r="R89" t="n">
-        <v>6783224</v>
+        <v>6783272</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9424,7 +9424,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129963692</v>
+        <v>129963710</v>
       </c>
       <c r="B90" t="n">
         <v>79707</v>
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>435238</v>
+        <v>435047</v>
       </c>
       <c r="R90" t="n">
-        <v>6783256</v>
+        <v>6783384</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9521,10 +9521,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129963825</v>
+        <v>129963691</v>
       </c>
       <c r="B91" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>435247</v>
+        <v>435115</v>
       </c>
       <c r="R91" t="n">
-        <v>6783126</v>
+        <v>6783224</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129963832</v>
+        <v>129963692</v>
       </c>
       <c r="B92" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9629,21 +9629,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9653,10 +9653,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435150</v>
+        <v>435238</v>
       </c>
       <c r="R92" t="n">
-        <v>6783272</v>
+        <v>6783256</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11913,54 +11913,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129963790</v>
+        <v>129963706</v>
       </c>
       <c r="B115" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>435100</v>
+        <v>435067</v>
       </c>
       <c r="R115" t="n">
-        <v>6783252</v>
+        <v>6783353</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12001,7 +11992,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12020,7 +12010,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129963706</v>
+        <v>129963693</v>
       </c>
       <c r="B116" t="n">
         <v>79707</v>
@@ -12055,10 +12045,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>435067</v>
+        <v>435260</v>
       </c>
       <c r="R116" t="n">
-        <v>6783353</v>
+        <v>6783290</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12117,7 +12107,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129963693</v>
+        <v>129963698</v>
       </c>
       <c r="B117" t="n">
         <v>79707</v>
@@ -12152,10 +12142,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>435260</v>
+        <v>435103</v>
       </c>
       <c r="R117" t="n">
-        <v>6783290</v>
+        <v>6783246</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12214,10 +12204,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129963698</v>
+        <v>129963740</v>
       </c>
       <c r="B118" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12225,34 +12215,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435103</v>
+        <v>435041</v>
       </c>
       <c r="R118" t="n">
-        <v>6783246</v>
+        <v>6783374</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12311,40 +12309,41 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129963740</v>
+        <v>129963790</v>
       </c>
       <c r="B119" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -12354,10 +12353,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435041</v>
+        <v>435100</v>
       </c>
       <c r="R119" t="n">
-        <v>6783374</v>
+        <v>6783252</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12398,6 +12397,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12513,10 +12513,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129963741</v>
+        <v>129963845</v>
       </c>
       <c r="B121" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12524,42 +12524,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435038</v>
+        <v>435002</v>
       </c>
       <c r="R121" t="n">
-        <v>6783388</v>
+        <v>6783412</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12618,41 +12610,40 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129963780</v>
+        <v>129963741</v>
       </c>
       <c r="B122" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -12662,10 +12653,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>435085</v>
+        <v>435038</v>
       </c>
       <c r="R122" t="n">
-        <v>6783160</v>
+        <v>6783388</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12706,7 +12697,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12725,45 +12715,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129963751</v>
+        <v>129963780</v>
       </c>
       <c r="B123" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434998</v>
+        <v>435085</v>
       </c>
       <c r="R123" t="n">
-        <v>6783271</v>
+        <v>6783160</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12804,6 +12803,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12822,10 +12822,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129963722</v>
+        <v>129963751</v>
       </c>
       <c r="B124" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12833,21 +12833,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>435197</v>
+        <v>434998</v>
       </c>
       <c r="R124" t="n">
-        <v>6783294</v>
+        <v>6783271</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129963845</v>
+        <v>129963722</v>
       </c>
       <c r="B125" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12930,21 +12930,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12954,10 +12954,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435002</v>
+        <v>435197</v>
       </c>
       <c r="R125" t="n">
-        <v>6783412</v>
+        <v>6783294</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 7913-2025 artfynd.xlsx
+++ b/artfynd/A 7913-2025 artfynd.xlsx
@@ -1354,40 +1354,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129963742</v>
+        <v>129963785</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1397,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434938</v>
+        <v>435286</v>
       </c>
       <c r="R9" t="n">
-        <v>6783317</v>
+        <v>6783280</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1441,6 +1442,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1459,41 +1461,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129963785</v>
+        <v>129963742</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1503,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435286</v>
+        <v>434938</v>
       </c>
       <c r="R10" t="n">
-        <v>6783280</v>
+        <v>6783317</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,7 +1548,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -7342,45 +7342,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129963688</v>
+        <v>129963748</v>
       </c>
       <c r="B69" t="n">
-        <v>79707</v>
+        <v>56933</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435226</v>
+        <v>435072</v>
       </c>
       <c r="R69" t="n">
-        <v>6783162</v>
+        <v>6783347</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7439,10 +7447,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129963837</v>
+        <v>129963735</v>
       </c>
       <c r="B70" t="n">
-        <v>79088</v>
+        <v>57898</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7450,34 +7458,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435094</v>
+        <v>435028</v>
       </c>
       <c r="R70" t="n">
-        <v>6783352</v>
+        <v>6783350</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7536,7 +7552,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129963764</v>
+        <v>129963761</v>
       </c>
       <c r="B71" t="n">
         <v>78846</v>
@@ -7571,10 +7587,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435059</v>
+        <v>435140</v>
       </c>
       <c r="R71" t="n">
-        <v>6783248</v>
+        <v>6783272</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7633,53 +7649,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129963748</v>
+        <v>129963764</v>
       </c>
       <c r="B72" t="n">
-        <v>56933</v>
+        <v>78846</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435072</v>
+        <v>435059</v>
       </c>
       <c r="R72" t="n">
-        <v>6783347</v>
+        <v>6783248</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7738,10 +7746,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129963735</v>
+        <v>129963728</v>
       </c>
       <c r="B73" t="n">
-        <v>57898</v>
+        <v>79678</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7749,42 +7757,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435028</v>
+        <v>435152</v>
       </c>
       <c r="R73" t="n">
-        <v>6783350</v>
+        <v>6783393</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129963761</v>
+        <v>129963688</v>
       </c>
       <c r="B74" t="n">
-        <v>78846</v>
+        <v>79707</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7854,21 +7854,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7878,10 +7878,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435140</v>
+        <v>435226</v>
       </c>
       <c r="R74" t="n">
-        <v>6783272</v>
+        <v>6783162</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7940,10 +7940,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129963728</v>
+        <v>129963837</v>
       </c>
       <c r="B75" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7951,21 +7951,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435152</v>
+        <v>435094</v>
       </c>
       <c r="R75" t="n">
-        <v>6783393</v>
+        <v>6783352</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8730,35 +8730,44 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129963713</v>
+        <v>129963779</v>
       </c>
       <c r="B83" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
@@ -8768,7 +8777,7 @@
         <v>434963</v>
       </c>
       <c r="R83" t="n">
-        <v>6783297</v>
+        <v>6783366</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8809,6 +8818,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8827,10 +8837,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129963847</v>
+        <v>129963713</v>
       </c>
       <c r="B84" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8838,21 +8848,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8862,10 +8872,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435018</v>
+        <v>434963</v>
       </c>
       <c r="R84" t="n">
-        <v>6783344</v>
+        <v>6783297</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8924,7 +8934,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129963829</v>
+        <v>129963847</v>
       </c>
       <c r="B85" t="n">
         <v>79088</v>
@@ -8959,10 +8969,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435142</v>
+        <v>435018</v>
       </c>
       <c r="R85" t="n">
-        <v>6783234</v>
+        <v>6783344</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8995,11 +9005,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9026,54 +9031,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129963779</v>
+        <v>129963829</v>
       </c>
       <c r="B86" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434963</v>
+        <v>435142</v>
       </c>
       <c r="R86" t="n">
-        <v>6783366</v>
+        <v>6783234</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9108,13 +9104,17 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9822,10 +9822,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129963826</v>
+        <v>129963686</v>
       </c>
       <c r="B94" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9833,21 +9833,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>435250</v>
+        <v>435088</v>
       </c>
       <c r="R94" t="n">
-        <v>6783158</v>
+        <v>6783097</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9919,7 +9919,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129963686</v>
+        <v>129963711</v>
       </c>
       <c r="B95" t="n">
         <v>79707</v>
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>435088</v>
+        <v>435000</v>
       </c>
       <c r="R95" t="n">
-        <v>6783097</v>
+        <v>6783432</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10016,7 +10016,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129963711</v>
+        <v>129963680</v>
       </c>
       <c r="B96" t="n">
         <v>79707</v>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>435000</v>
+        <v>434999</v>
       </c>
       <c r="R96" t="n">
-        <v>6783432</v>
+        <v>6783278</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129963680</v>
+        <v>129963802</v>
       </c>
       <c r="B97" t="n">
-        <v>79707</v>
+        <v>78845</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10124,21 +10124,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10148,10 +10148,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434999</v>
+        <v>435056</v>
       </c>
       <c r="R97" t="n">
-        <v>6783278</v>
+        <v>6783229</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129963802</v>
+        <v>129963826</v>
       </c>
       <c r="B98" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>435056</v>
+        <v>435250</v>
       </c>
       <c r="R98" t="n">
-        <v>6783229</v>
+        <v>6783158</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10711,10 +10711,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129963687</v>
+        <v>129963752</v>
       </c>
       <c r="B103" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10722,21 +10722,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>435243</v>
+        <v>435046</v>
       </c>
       <c r="R103" t="n">
-        <v>6783165</v>
+        <v>6783227</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129963712</v>
+        <v>129963754</v>
       </c>
       <c r="B104" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10819,21 +10819,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434998</v>
+        <v>435094</v>
       </c>
       <c r="R104" t="n">
-        <v>6783407</v>
+        <v>6783192</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10905,10 +10905,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129963747</v>
+        <v>129963687</v>
       </c>
       <c r="B105" t="n">
-        <v>56313</v>
+        <v>79707</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10916,42 +10916,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>206004</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>435173</v>
+        <v>435243</v>
       </c>
       <c r="R105" t="n">
-        <v>6783096</v>
+        <v>6783165</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11010,10 +11002,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129963821</v>
+        <v>129963712</v>
       </c>
       <c r="B106" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11021,21 +11013,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11045,10 +11037,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>435042</v>
+        <v>434998</v>
       </c>
       <c r="R106" t="n">
-        <v>6783226</v>
+        <v>6783407</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11107,54 +11099,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129963791</v>
+        <v>129963821</v>
       </c>
       <c r="B107" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>435076</v>
+        <v>435042</v>
       </c>
       <c r="R107" t="n">
-        <v>6783364</v>
+        <v>6783226</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11195,7 +11178,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11214,45 +11196,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129963752</v>
+        <v>129963791</v>
       </c>
       <c r="B108" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>435046</v>
+        <v>435076</v>
       </c>
       <c r="R108" t="n">
-        <v>6783227</v>
+        <v>6783364</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11293,6 +11284,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11311,10 +11303,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129963754</v>
+        <v>129963747</v>
       </c>
       <c r="B109" t="n">
-        <v>78846</v>
+        <v>56313</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11322,34 +11314,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>206004</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Lill-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>435094</v>
+        <v>435173</v>
       </c>
       <c r="R109" t="n">
-        <v>6783192</v>
+        <v>6783096</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
